--- a/companies.xlsx
+++ b/companies.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -48,6 +48,12 @@
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="00C00000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00B8860B"/>
       <sz val="10"/>
     </font>
     <font>
@@ -121,11 +127,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -133,11 +137,13 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -220,14 +226,14 @@
     <author>JobTracker</author>
   </authors>
   <commentList>
+    <comment ref="A1" authorId="0" shapeId="0">
+      <text>
+        <t>Gold bold names: auto-verified via guessed token, not hand-checked. Fine to leave, worth a glance.</t>
+      </text>
+    </comment>
     <comment ref="C1" authorId="0" shapeId="0">
       <text>
-        <t>Filter this column to see Startups / Unicorns / MNCs / IT Services separately.</t>
-      </text>
-    </comment>
-    <comment ref="G1" authorId="0" shapeId="0">
-      <text>
-        <t>Only 'Active' rows are scraped. Set to Inactive to skip a company.</t>
+        <t>Filter to see Startup / Unicorn / MNC / IT Services separately.</t>
       </text>
     </comment>
   </commentList>
@@ -531,7 +537,7 @@
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="62" customWidth="1" min="8" max="8"/>
   </cols>
@@ -604,13 +610,17 @@
           <t>Gurugram</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr"/>
+      <c r="F2" s="2" t="n">
+        <v/>
+      </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr"/>
+      <c r="H2" s="2" t="n">
+        <v/>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -638,13 +648,17 @@
           <t>Chennai</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr"/>
+      <c r="F3" s="2" t="n">
+        <v/>
+      </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="n">
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -672,13 +686,17 @@
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr"/>
+      <c r="F4" s="2" t="n">
+        <v/>
+      </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="n">
+        <v/>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -706,13 +724,17 @@
           <t>Gurugram</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr"/>
+      <c r="F5" s="2" t="n">
+        <v/>
+      </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="n">
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -740,13 +762,17 @@
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr"/>
+      <c r="F6" s="2" t="n">
+        <v/>
+      </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="n">
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -774,13 +800,17 @@
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr"/>
+      <c r="F7" s="2" t="n">
+        <v/>
+      </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="n">
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -808,13 +838,17 @@
           <t>Hyderabad</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr"/>
+      <c r="F8" s="2" t="n">
+        <v/>
+      </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="n">
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -842,13 +876,17 @@
           <t>Delhi</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr"/>
+      <c r="F9" s="2" t="n">
+        <v/>
+      </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="n">
+        <v/>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -876,13 +914,17 @@
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr"/>
+      <c r="F10" s="2" t="n">
+        <v/>
+      </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="n">
+        <v/>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -910,13 +952,17 @@
           <t>Chennai</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr"/>
+      <c r="F11" s="2" t="n">
+        <v/>
+      </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="n">
+        <v/>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -926,7 +972,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>https://fi.money/careers</t>
+          <t>https://jobs.lever.co/epifi</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -944,13 +990,19 @@
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr"/>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>lever</t>
+        </is>
+      </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="n">
+        <v/>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -978,13 +1030,17 @@
           <t>Mumbai</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr"/>
+      <c r="F13" s="2" t="n">
+        <v/>
+      </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="n">
+        <v/>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -1012,13 +1068,17 @@
           <t>Mumbai</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr"/>
+      <c r="F14" s="2" t="n">
+        <v/>
+      </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="n">
+        <v/>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -1046,23 +1106,27 @@
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr"/>
+      <c r="F15" s="2" t="n">
+        <v/>
+      </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="n">
+        <v/>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>ideaForge</t>
+          <t>IDfy</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>https://ideaforgetech.com/careers</t>
+          <t>https://www.idfy.com/careers/</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1072,7 +1136,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Drones</t>
+          <t>Fintech</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1080,23 +1144,27 @@
           <t>Mumbai</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr"/>
+      <c r="F16" s="2" t="n">
+        <v/>
+      </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="n">
+        <v/>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>IDfy</t>
+          <t>INDmoney</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>https://www.idfy.com/careers/</t>
+          <t>https://www.indmoney.com/careers</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1111,16 +1179,20 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Mumbai</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr"/>
+          <t>Gurugram</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="n">
+        <v/>
+      </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="n">
+        <v/>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -1148,23 +1220,27 @@
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr"/>
+      <c r="F18" s="2" t="n">
+        <v/>
+      </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="n">
+        <v/>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>INDmoney</t>
+          <t>Jupiter</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>https://www.indmoney.com/careers</t>
+          <t>https://jupiter.money/careers/</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1179,26 +1255,30 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Gurugram</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr"/>
+          <t>Bengaluru</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="n">
+        <v/>
+      </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="n">
+        <v/>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Jupiter</t>
+          <t>Kaleyra</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>https://jupiter.money/careers/</t>
+          <t>https://www.kaleyra.com/careers/</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1208,7 +1288,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Fintech</t>
+          <t>CPaaS</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1216,23 +1296,27 @@
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr"/>
+      <c r="F20" s="2" t="n">
+        <v/>
+      </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="n">
+        <v/>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Kaleyra</t>
+          <t>Keka</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>https://www.kaleyra.com/careers/</t>
+          <t>https://www.keka.com/careers</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1242,31 +1326,35 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>CPaaS</t>
+          <t>HR Tech</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr"/>
+          <t>Hyderabad</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="n">
+        <v/>
+      </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="n">
+        <v/>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Keka</t>
+          <t>Kissflow</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>https://www.keka.com/careers</t>
+          <t>https://kissflow.com/careers/</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -1276,31 +1364,35 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>HR Tech</t>
+          <t>SaaS</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Hyderabad</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr"/>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v/>
+      </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="n">
+        <v/>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>Kissflow</t>
+          <t>Kiwi</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>https://kissflow.com/careers/</t>
+          <t>https://www.gokiwi.in/careers</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -1310,31 +1402,35 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>SaaS</t>
+          <t>Fintech</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Chennai</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr"/>
+          <t>Bengaluru</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="n">
+        <v/>
+      </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr"/>
+      <c r="H23" s="2" t="n">
+        <v/>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Kiwi</t>
+          <t>Krutrim</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>https://www.gokiwi.in/careers</t>
+          <t>https://www.olakrutrim.com/careers</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -1344,7 +1440,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Fintech</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -1352,23 +1448,27 @@
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr"/>
+      <c r="F24" s="2" t="n">
+        <v/>
+      </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="n">
+        <v/>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>Krutrim</t>
+          <t>Kuku FM</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>https://www.olakrutrim.com/careers</t>
+          <t>https://kukufm.com/careers</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -1378,31 +1478,35 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>Audio</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr"/>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="n">
+        <v/>
+      </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr"/>
+      <c r="H25" s="2" t="n">
+        <v/>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Kuku FM</t>
+          <t>Lendingkart</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>https://kukufm.com/careers</t>
+          <t>https://careers.smartrecruiters.com/lendingkart</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -1412,31 +1516,37 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Audio</t>
+          <t>Fintech</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Mumbai</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr"/>
+          <t>Ahmedabad</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>smartrecruiters</t>
+        </is>
+      </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr"/>
+      <c r="H26" s="2" t="n">
+        <v/>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>Lendingkart</t>
+          <t>Locus</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>https://www.lendingkart.com/careers/</t>
+          <t>https://locus.sh/careers/</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -1446,31 +1556,35 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Fintech</t>
+          <t>Logistics SaaS</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Ahmedabad</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr"/>
+          <t>Bengaluru</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="n">
+        <v/>
+      </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H27" s="2" t="inlineStr"/>
+      <c r="H27" s="2" t="n">
+        <v/>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Locus</t>
+          <t>Log9 Materials</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>https://locus.sh/careers/</t>
+          <t>https://www.log9materials.com/careers</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -1480,7 +1594,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Logistics SaaS</t>
+          <t>CleanTech</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1488,23 +1602,27 @@
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr"/>
+      <c r="F28" s="2" t="n">
+        <v/>
+      </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr"/>
+      <c r="H28" s="2" t="n">
+        <v/>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>Log9 Materials</t>
+          <t>Masai School</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>https://www.log9materials.com/careers</t>
+          <t>https://www.masaischool.com/careers</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -1514,7 +1632,7 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>CleanTech</t>
+          <t>EdTech</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -1522,23 +1640,27 @@
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr"/>
+      <c r="F29" s="2" t="n">
+        <v/>
+      </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr"/>
+      <c r="H29" s="2" t="n">
+        <v/>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>Masai School</t>
+          <t>Newton School</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>https://www.masaischool.com/careers</t>
+          <t>https://careers.smartrecruiters.com/newtonschool</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -1556,23 +1678,29 @@
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr"/>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>smartrecruiters</t>
+        </is>
+      </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H30" s="2" t="inlineStr"/>
+      <c r="H30" s="2" t="n">
+        <v/>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>Newton School</t>
+          <t>Open Financial</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>https://www.newtonschool.co/careers</t>
+          <t>https://open.money/careers</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -1582,7 +1710,7 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>EdTech</t>
+          <t>Fintech</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -1590,23 +1718,27 @@
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr"/>
+      <c r="F31" s="2" t="n">
+        <v/>
+      </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H31" s="2" t="inlineStr"/>
+      <c r="H31" s="2" t="n">
+        <v/>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>Open Financial</t>
+          <t>Pixxel</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>https://open.money/careers</t>
+          <t>https://www.pixxel.space/careers</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -1616,7 +1748,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Fintech</t>
+          <t>Space</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -1624,23 +1756,27 @@
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr"/>
+      <c r="F32" s="2" t="n">
+        <v/>
+      </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H32" s="2" t="inlineStr"/>
+      <c r="H32" s="2" t="n">
+        <v/>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>Pixxel</t>
+          <t>Plivo</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>https://www.pixxel.space/careers</t>
+          <t>https://www.plivo.com/careers/</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -1650,7 +1786,7 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Space</t>
+          <t>CPaaS</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -1658,23 +1794,27 @@
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr"/>
+      <c r="F33" s="2" t="n">
+        <v/>
+      </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H33" s="2" t="inlineStr"/>
+      <c r="H33" s="2" t="n">
+        <v/>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>Plivo</t>
+          <t>Portea Medical</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>https://www.plivo.com/careers/</t>
+          <t>https://www.portea.com/careers/</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -1684,7 +1824,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>CPaaS</t>
+          <t>HealthTech</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -1692,23 +1832,27 @@
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr"/>
+      <c r="F34" s="2" t="n">
+        <v/>
+      </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H34" s="2" t="inlineStr"/>
+      <c r="H34" s="2" t="n">
+        <v/>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>Portea Medical</t>
+          <t>Pratilipi</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>https://www.portea.com/careers/</t>
+          <t>https://pratilipi.com/careers</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -1718,7 +1862,7 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>HealthTech</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -1726,23 +1870,27 @@
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr"/>
+      <c r="F35" s="2" t="n">
+        <v/>
+      </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H35" s="2" t="inlineStr"/>
+      <c r="H35" s="2" t="n">
+        <v/>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Pratilipi</t>
+          <t>Qure.ai</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>https://pratilipi.com/careers</t>
+          <t>https://www.qure.ai/careers</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -1752,31 +1900,35 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>AI Health</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr"/>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="n">
+        <v/>
+      </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H36" s="2" t="inlineStr"/>
+      <c r="H36" s="2" t="n">
+        <v/>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>Qure.ai</t>
+          <t>Rocketlane</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>https://www.qure.ai/careers</t>
+          <t>https://www.rocketlane.com/careers</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -1786,31 +1938,35 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>AI Health</t>
+          <t>SaaS</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>Mumbai</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr"/>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="n">
+        <v/>
+      </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H37" s="2" t="inlineStr"/>
+      <c r="H37" s="2" t="n">
+        <v/>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>Rocketlane</t>
+          <t>Rupeek</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>https://www.rocketlane.com/careers</t>
+          <t>https://rupeek.com/careers</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -1820,31 +1976,35 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>SaaS</t>
+          <t>Fintech</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Chennai</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr"/>
+          <t>Bengaluru</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="n">
+        <v/>
+      </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H38" s="2" t="inlineStr"/>
+      <c r="H38" s="2" t="n">
+        <v/>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>Rupeek</t>
+          <t>Sarvam AI</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>https://rupeek.com/careers</t>
+          <t>https://jobs.ashbyhq.com/sarvam</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -1854,7 +2014,7 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Fintech</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -1862,23 +2022,29 @@
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr"/>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>ashby</t>
+        </is>
+      </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H39" s="2" t="inlineStr"/>
+      <c r="H39" s="2" t="n">
+        <v/>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Sarvam AI</t>
+          <t>Scaler</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>https://www.sarvam.ai/careers</t>
+          <t>https://www.scaler.com/careers/</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -1888,7 +2054,7 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>EdTech</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -1896,23 +2062,27 @@
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr"/>
+      <c r="F40" s="2" t="n">
+        <v/>
+      </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H40" s="2" t="inlineStr"/>
+      <c r="H40" s="2" t="n">
+        <v/>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>Scaler</t>
+          <t>Setu</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>https://www.scaler.com/careers/</t>
+          <t>https://setu.co/careers</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -1922,7 +2092,7 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>EdTech</t>
+          <t>Fintech</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -1930,23 +2100,27 @@
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr"/>
+      <c r="F41" s="2" t="n">
+        <v/>
+      </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H41" s="2" t="inlineStr"/>
+      <c r="H41" s="2" t="n">
+        <v/>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Setu</t>
+          <t>Shipsy</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>https://setu.co/careers</t>
+          <t>https://careers.smartrecruiters.com/shipsy</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -1956,31 +2130,37 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Fintech</t>
+          <t>Logistics SaaS</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr"/>
+          <t>Gurugram</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>smartrecruiters</t>
+        </is>
+      </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H42" s="2" t="inlineStr"/>
+      <c r="H42" s="2" t="n">
+        <v/>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>Shipsy</t>
+          <t>Signzy</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>https://shipsy.io/careers/</t>
+          <t>https://www.signzy.com/careers/</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -1990,31 +2170,35 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Logistics SaaS</t>
+          <t>Fintech</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>Gurugram</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr"/>
+          <t>Bengaluru</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="n">
+        <v/>
+      </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H43" s="2" t="inlineStr"/>
+      <c r="H43" s="2" t="n">
+        <v/>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>Signzy</t>
+          <t>Skyroot Aerospace</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>https://www.signzy.com/careers/</t>
+          <t>https://skyroot.in/careers.html</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -2024,31 +2208,35 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Fintech</t>
+          <t>Space</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr"/>
+          <t>Hyderabad</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="n">
+        <v/>
+      </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H44" s="2" t="inlineStr"/>
+      <c r="H44" s="2" t="n">
+        <v/>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>Skyroot Aerospace</t>
+          <t>Slice</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>https://skyroot.in/careers.html</t>
+          <t>https://www.sliceit.com/careers</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -2058,31 +2246,35 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Space</t>
+          <t>Fintech</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>Hyderabad</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr"/>
+          <t>Bengaluru</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="n">
+        <v/>
+      </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H45" s="2" t="inlineStr"/>
+      <c r="H45" s="2" t="n">
+        <v/>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>Slice</t>
+          <t>Smallcase</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>https://www.sliceit.com/careers</t>
+          <t>https://www.smallcase.com/careers</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -2100,23 +2292,27 @@
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr"/>
+      <c r="F46" s="2" t="n">
+        <v/>
+      </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H46" s="2" t="inlineStr"/>
+      <c r="H46" s="2" t="n">
+        <v/>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>Smallcase</t>
+          <t>Testbook</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>https://www.smallcase.com/careers</t>
+          <t>https://testbook.com/careers</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -2126,31 +2322,35 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Fintech</t>
+          <t>EdTech</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="F47" s="2" t="inlineStr"/>
+          <t>Navi Mumbai</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="n">
+        <v/>
+      </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H47" s="2" t="inlineStr"/>
+      <c r="H47" s="2" t="n">
+        <v/>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>Testbook</t>
+          <t>Tonbo Imaging</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>https://testbook.com/careers</t>
+          <t>https://www.tonboimaging.com/careers/</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -2160,31 +2360,35 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>EdTech</t>
+          <t>Defence Tech</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Navi Mumbai</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="inlineStr"/>
+          <t>Bengaluru</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="n">
+        <v/>
+      </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H48" s="2" t="inlineStr"/>
+      <c r="H48" s="2" t="n">
+        <v/>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>Tonbo Imaging</t>
+          <t>Unicommerce</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>https://www.tonboimaging.com/careers/</t>
+          <t>https://unicommerce.com/careers/</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -2194,31 +2398,35 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>Defence Tech</t>
+          <t>E-com SaaS</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="F49" s="2" t="inlineStr"/>
+          <t>Noida</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="n">
+        <v/>
+      </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H49" s="2" t="inlineStr"/>
+      <c r="H49" s="2" t="n">
+        <v/>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>Unicommerce</t>
+          <t>Vymo</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>https://unicommerce.com/careers/</t>
+          <t>https://getvymo.com/careers/</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -2228,31 +2436,35 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>E-com SaaS</t>
+          <t>SaaS</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Noida</t>
-        </is>
-      </c>
-      <c r="F50" s="2" t="inlineStr"/>
+          <t>Bengaluru</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="n">
+        <v/>
+      </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H50" s="2" t="inlineStr"/>
+      <c r="H50" s="2" t="n">
+        <v/>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>Vymo</t>
+          <t>Wingify</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>https://getvymo.com/careers/</t>
+          <t>https://wingify.com/careers</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -2262,31 +2474,35 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>SaaS</t>
+          <t>MarTech</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="F51" s="2" t="inlineStr"/>
+          <t>Delhi</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="n">
+        <v/>
+      </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H51" s="2" t="inlineStr"/>
+      <c r="H51" s="2" t="n">
+        <v/>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>Wingify</t>
+          <t>Yulu</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>https://wingify.com/careers</t>
+          <t>https://www.yulu.bike/careers/</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -2296,31 +2512,35 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>MarTech</t>
+          <t>Mobility</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Delhi</t>
-        </is>
-      </c>
-      <c r="F52" s="2" t="inlineStr"/>
+          <t>Bengaluru</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="n">
+        <v/>
+      </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H52" s="2" t="inlineStr"/>
+      <c r="H52" s="2" t="n">
+        <v/>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>Yulu</t>
+          <t>Zluri</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>https://www.yulu.bike/careers/</t>
+          <t>https://www.zluri.com/careers</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -2330,7 +2550,7 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Mobility</t>
+          <t>SaaS</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -2338,23 +2558,27 @@
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr"/>
+      <c r="F53" s="2" t="n">
+        <v/>
+      </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H53" s="2" t="inlineStr"/>
+      <c r="H53" s="2" t="n">
+        <v/>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>Zluri</t>
+          <t>ideaForge</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>https://www.zluri.com/careers</t>
+          <t>https://ideaforgetech.com/careers</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -2364,21 +2588,25 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>SaaS</t>
+          <t>Drones</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="F54" s="2" t="inlineStr"/>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="n">
+        <v/>
+      </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H54" s="2" t="inlineStr"/>
+      <c r="H54" s="2" t="n">
+        <v/>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
@@ -2406,13 +2634,17 @@
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="F55" s="4" t="inlineStr"/>
+      <c r="F55" s="4" t="n">
+        <v/>
+      </c>
       <c r="G55" s="4" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H55" s="4" t="inlineStr"/>
+      <c r="H55" s="4" t="n">
+        <v/>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
@@ -2440,13 +2672,17 @@
           <t>Mumbai</t>
         </is>
       </c>
-      <c r="F56" s="4" t="inlineStr"/>
+      <c r="F56" s="4" t="n">
+        <v/>
+      </c>
       <c r="G56" s="4" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H56" s="4" t="inlineStr"/>
+      <c r="H56" s="4" t="n">
+        <v/>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
@@ -2474,13 +2710,17 @@
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="F57" s="4" t="inlineStr"/>
+      <c r="F57" s="4" t="n">
+        <v/>
+      </c>
       <c r="G57" s="4" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H57" s="4" t="inlineStr"/>
+      <c r="H57" s="4" t="n">
+        <v/>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
@@ -2490,7 +2730,7 @@
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>https://atlan.com/careers/</t>
+          <t>https://jobs.ashbyhq.com/atlan</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
@@ -2508,13 +2748,19 @@
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="F58" s="4" t="inlineStr"/>
+      <c r="F58" s="4" t="inlineStr">
+        <is>
+          <t>ashby</t>
+        </is>
+      </c>
       <c r="G58" s="4" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H58" s="4" t="inlineStr"/>
+      <c r="H58" s="4" t="n">
+        <v/>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
@@ -2542,13 +2788,17 @@
           <t>Delhi</t>
         </is>
       </c>
-      <c r="F59" s="4" t="inlineStr"/>
+      <c r="F59" s="4" t="n">
+        <v/>
+      </c>
       <c r="G59" s="4" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H59" s="4" t="inlineStr"/>
+      <c r="H59" s="4" t="n">
+        <v/>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
@@ -2576,13 +2826,17 @@
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="F60" s="4" t="inlineStr"/>
+      <c r="F60" s="4" t="n">
+        <v/>
+      </c>
       <c r="G60" s="4" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H60" s="4" t="inlineStr"/>
+      <c r="H60" s="4" t="n">
+        <v/>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
@@ -2610,13 +2864,17 @@
           <t>Gurugram</t>
         </is>
       </c>
-      <c r="F61" s="4" t="inlineStr"/>
+      <c r="F61" s="4" t="n">
+        <v/>
+      </c>
       <c r="G61" s="4" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H61" s="4" t="inlineStr"/>
+      <c r="H61" s="4" t="n">
+        <v/>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
@@ -2644,23 +2902,27 @@
           <t>Mumbai</t>
         </is>
       </c>
-      <c r="F62" s="4" t="inlineStr"/>
+      <c r="F62" s="4" t="n">
+        <v/>
+      </c>
       <c r="G62" s="4" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H62" s="4" t="inlineStr"/>
+      <c r="H62" s="4" t="n">
+        <v/>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>Capillary Technologies</t>
+          <t>CRED</t>
         </is>
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>https://www.capillarytech.com/careers/</t>
+          <t>https://careers.cred.club/</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
@@ -2670,7 +2932,7 @@
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>MarTech</t>
+          <t>Fintech</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr">
@@ -2678,23 +2940,27 @@
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="F63" s="4" t="inlineStr"/>
+      <c r="F63" s="4" t="n">
+        <v/>
+      </c>
       <c r="G63" s="4" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H63" s="4" t="inlineStr"/>
+      <c r="H63" s="4" t="n">
+        <v/>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>CarDekho</t>
+          <t>Capillary Technologies</t>
         </is>
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>https://www.cardekho.com/careers</t>
+          <t>https://www.capillarytech.com/careers/</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
@@ -2704,31 +2970,35 @@
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>AutoTech</t>
+          <t>MarTech</t>
         </is>
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>Jaipur</t>
-        </is>
-      </c>
-      <c r="F64" s="4" t="inlineStr"/>
+          <t>Bengaluru</t>
+        </is>
+      </c>
+      <c r="F64" s="4" t="n">
+        <v/>
+      </c>
       <c r="G64" s="4" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H64" s="4" t="inlineStr"/>
+      <c r="H64" s="4" t="n">
+        <v/>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>Cars24</t>
+          <t>CarDekho</t>
         </is>
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>https://www.cars24.com/careers/</t>
+          <t>https://www.cardekho.com/careers</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
@@ -2743,26 +3013,30 @@
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>Gurugram</t>
-        </is>
-      </c>
-      <c r="F65" s="4" t="inlineStr"/>
+          <t>Jaipur</t>
+        </is>
+      </c>
+      <c r="F65" s="4" t="n">
+        <v/>
+      </c>
       <c r="G65" s="4" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H65" s="4" t="inlineStr"/>
+      <c r="H65" s="4" t="n">
+        <v/>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>Chargebee</t>
+          <t>Cars24</t>
         </is>
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>https://www.chargebee.com/careers/</t>
+          <t>https://careers.smartrecruiters.com/cars24</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
@@ -2772,31 +3046,37 @@
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>SaaS Fintech</t>
+          <t>AutoTech</t>
         </is>
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>Chennai</t>
-        </is>
-      </c>
-      <c r="F66" s="4" t="inlineStr"/>
+          <t>Gurugram</t>
+        </is>
+      </c>
+      <c r="F66" s="4" t="inlineStr">
+        <is>
+          <t>smartrecruiters</t>
+        </is>
+      </c>
       <c r="G66" s="4" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H66" s="4" t="inlineStr"/>
+      <c r="H66" s="4" t="n">
+        <v/>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>Cleartrip</t>
+          <t>Chargebee</t>
         </is>
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>https://www.cleartrip.com/careers</t>
+          <t>https://www.chargebee.com/careers/</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
@@ -2806,31 +3086,35 @@
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>Travel</t>
+          <t>SaaS Fintech</t>
         </is>
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="F67" s="4" t="inlineStr"/>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="F67" s="4" t="n">
+        <v/>
+      </c>
       <c r="G67" s="4" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H67" s="4" t="inlineStr"/>
+      <c r="H67" s="4" t="n">
+        <v/>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>CleverTap</t>
+          <t>Cleartrip</t>
         </is>
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>https://clevertap.com/careers/</t>
+          <t>https://www.cleartrip.com/careers</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
@@ -2840,31 +3124,35 @@
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>MarTech</t>
+          <t>Travel</t>
         </is>
       </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t>Mumbai</t>
-        </is>
-      </c>
-      <c r="F68" s="4" t="inlineStr"/>
+          <t>Bengaluru</t>
+        </is>
+      </c>
+      <c r="F68" s="4" t="n">
+        <v/>
+      </c>
       <c r="G68" s="4" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H68" s="4" t="inlineStr"/>
+      <c r="H68" s="4" t="n">
+        <v/>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>CRED</t>
+          <t>CleverTap</t>
         </is>
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>https://careers.cred.club/</t>
+          <t>https://clevertap.com/careers/</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
@@ -2874,21 +3162,25 @@
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>Fintech</t>
+          <t>MarTech</t>
         </is>
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="F69" s="4" t="inlineStr"/>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="F69" s="4" t="n">
+        <v/>
+      </c>
       <c r="G69" s="4" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H69" s="4" t="inlineStr"/>
+      <c r="H69" s="4" t="n">
+        <v/>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
@@ -2916,13 +3208,17 @@
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="F70" s="4" t="inlineStr"/>
+      <c r="F70" s="4" t="n">
+        <v/>
+      </c>
       <c r="G70" s="4" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H70" s="4" t="inlineStr"/>
+      <c r="H70" s="4" t="n">
+        <v/>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
@@ -2950,13 +3246,17 @@
           <t>Hyderabad</t>
         </is>
       </c>
-      <c r="F71" s="4" t="inlineStr"/>
+      <c r="F71" s="4" t="n">
+        <v/>
+      </c>
       <c r="G71" s="4" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H71" s="4" t="inlineStr"/>
+      <c r="H71" s="4" t="n">
+        <v/>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
@@ -2984,13 +3284,17 @@
           <t>Patna</t>
         </is>
       </c>
-      <c r="F72" s="4" t="inlineStr"/>
+      <c r="F72" s="4" t="n">
+        <v/>
+      </c>
       <c r="G72" s="4" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H72" s="4" t="inlineStr"/>
+      <c r="H72" s="4" t="n">
+        <v/>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
@@ -3018,13 +3322,17 @@
           <t>Gurugram</t>
         </is>
       </c>
-      <c r="F73" s="4" t="inlineStr"/>
+      <c r="F73" s="4" t="n">
+        <v/>
+      </c>
       <c r="G73" s="4" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H73" s="4" t="inlineStr"/>
+      <c r="H73" s="4" t="n">
+        <v/>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
@@ -3052,13 +3360,17 @@
           <t>Mumbai</t>
         </is>
       </c>
-      <c r="F74" s="4" t="inlineStr"/>
+      <c r="F74" s="4" t="n">
+        <v/>
+      </c>
       <c r="G74" s="4" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H74" s="4" t="inlineStr"/>
+      <c r="H74" s="4" t="n">
+        <v/>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
@@ -3068,7 +3380,7 @@
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>https://www.druva.com/about/careers</t>
+          <t>https://boards.greenhouse.io/druva</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
@@ -3086,13 +3398,19 @@
           <t>Pune</t>
         </is>
       </c>
-      <c r="F75" s="4" t="inlineStr"/>
+      <c r="F75" s="4" t="inlineStr">
+        <is>
+          <t>greenhouse</t>
+        </is>
+      </c>
       <c r="G75" s="4" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H75" s="4" t="inlineStr"/>
+      <c r="H75" s="4" t="n">
+        <v/>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
@@ -3120,13 +3438,17 @@
           <t>Mumbai</t>
         </is>
       </c>
-      <c r="F76" s="4" t="inlineStr"/>
+      <c r="F76" s="4" t="n">
+        <v/>
+      </c>
       <c r="G76" s="4" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H76" s="4" t="inlineStr"/>
+      <c r="H76" s="4" t="n">
+        <v/>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
@@ -3154,13 +3476,17 @@
           <t>Noida</t>
         </is>
       </c>
-      <c r="F77" s="4" t="inlineStr"/>
+      <c r="F77" s="4" t="n">
+        <v/>
+      </c>
       <c r="G77" s="4" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H77" s="4" t="inlineStr"/>
+      <c r="H77" s="4" t="n">
+        <v/>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
@@ -3188,13 +3514,17 @@
           <t>Pune</t>
         </is>
       </c>
-      <c r="F78" s="4" t="inlineStr"/>
+      <c r="F78" s="4" t="n">
+        <v/>
+      </c>
       <c r="G78" s="4" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H78" s="4" t="inlineStr"/>
+      <c r="H78" s="4" t="n">
+        <v/>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
@@ -3222,13 +3552,17 @@
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="F79" s="4" t="inlineStr"/>
+      <c r="F79" s="4" t="n">
+        <v/>
+      </c>
       <c r="G79" s="4" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H79" s="4" t="inlineStr"/>
+      <c r="H79" s="4" t="n">
+        <v/>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="4" t="inlineStr">
@@ -3256,13 +3590,17 @@
           <t>Mumbai</t>
         </is>
       </c>
-      <c r="F80" s="4" t="inlineStr"/>
+      <c r="F80" s="4" t="n">
+        <v/>
+      </c>
       <c r="G80" s="4" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H80" s="4" t="inlineStr"/>
+      <c r="H80" s="4" t="n">
+        <v/>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
@@ -3290,13 +3628,17 @@
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="F81" s="4" t="inlineStr"/>
+      <c r="F81" s="4" t="n">
+        <v/>
+      </c>
       <c r="G81" s="4" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H81" s="4" t="inlineStr"/>
+      <c r="H81" s="4" t="n">
+        <v/>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="4" t="inlineStr">
@@ -3324,13 +3666,17 @@
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="F82" s="4" t="inlineStr"/>
+      <c r="F82" s="4" t="n">
+        <v/>
+      </c>
       <c r="G82" s="4" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H82" s="4" t="inlineStr"/>
+      <c r="H82" s="4" t="n">
+        <v/>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
@@ -3340,7 +3686,7 @@
       </c>
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>https://groww.in/careers</t>
+          <t>https://boards.greenhouse.io/groww</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
@@ -3358,13 +3704,19 @@
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="F83" s="4" t="inlineStr"/>
+      <c r="F83" s="4" t="inlineStr">
+        <is>
+          <t>greenhouse</t>
+        </is>
+      </c>
       <c r="G83" s="4" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H83" s="4" t="inlineStr"/>
+      <c r="H83" s="4" t="n">
+        <v/>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="4" t="inlineStr">
@@ -3392,13 +3744,17 @@
           <t>Mumbai</t>
         </is>
       </c>
-      <c r="F84" s="4" t="inlineStr"/>
+      <c r="F84" s="4" t="n">
+        <v/>
+      </c>
       <c r="G84" s="4" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H84" s="4" t="inlineStr"/>
+      <c r="H84" s="4" t="n">
+        <v/>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
@@ -3426,13 +3782,17 @@
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="F85" s="4" t="inlineStr"/>
+      <c r="F85" s="4" t="n">
+        <v/>
+      </c>
       <c r="G85" s="4" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H85" s="4" t="inlineStr"/>
+      <c r="H85" s="4" t="n">
+        <v/>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="4" t="inlineStr">
@@ -3442,7 +3802,7 @@
       </c>
       <c r="B86" s="5" t="inlineStr">
         <is>
-          <t>https://www.highradius.com/careers/</t>
+          <t>https://boards.greenhouse.io/highradius</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
@@ -3460,13 +3820,19 @@
           <t>Hyderabad</t>
         </is>
       </c>
-      <c r="F86" s="4" t="inlineStr"/>
+      <c r="F86" s="4" t="inlineStr">
+        <is>
+          <t>greenhouse</t>
+        </is>
+      </c>
       <c r="G86" s="4" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H86" s="4" t="inlineStr"/>
+      <c r="H86" s="4" t="n">
+        <v/>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
@@ -3494,13 +3860,17 @@
           <t>Pune</t>
         </is>
       </c>
-      <c r="F87" s="4" t="inlineStr"/>
+      <c r="F87" s="4" t="n">
+        <v/>
+      </c>
       <c r="G87" s="4" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H87" s="4" t="inlineStr"/>
+      <c r="H87" s="4" t="n">
+        <v/>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="4" t="inlineStr">
@@ -3528,13 +3898,17 @@
           <t>Noida</t>
         </is>
       </c>
-      <c r="F88" s="4" t="inlineStr"/>
+      <c r="F88" s="4" t="n">
+        <v/>
+      </c>
       <c r="G88" s="4" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H88" s="4" t="inlineStr"/>
+      <c r="H88" s="4" t="n">
+        <v/>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
@@ -3544,7 +3918,7 @@
       </c>
       <c r="B89" s="5" t="inlineStr">
         <is>
-          <t>https://www.ixigo.com/careers</t>
+          <t>https://careers.smartrecruiters.com/ixigo</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
@@ -3562,13 +3936,19 @@
           <t>Gurugram</t>
         </is>
       </c>
-      <c r="F89" s="4" t="inlineStr"/>
+      <c r="F89" s="4" t="inlineStr">
+        <is>
+          <t>smartrecruiters</t>
+        </is>
+      </c>
       <c r="G89" s="4" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H89" s="4" t="inlineStr"/>
+      <c r="H89" s="4" t="n">
+        <v/>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="4" t="inlineStr">
@@ -3596,13 +3976,17 @@
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="F90" s="4" t="inlineStr"/>
+      <c r="F90" s="4" t="n">
+        <v/>
+      </c>
       <c r="G90" s="4" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H90" s="4" t="inlineStr"/>
+      <c r="H90" s="4" t="n">
+        <v/>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
@@ -3630,23 +4014,27 @@
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="F91" s="4" t="inlineStr"/>
+      <c r="F91" s="4" t="n">
+        <v/>
+      </c>
       <c r="G91" s="4" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H91" s="4" t="inlineStr"/>
+      <c r="H91" s="4" t="n">
+        <v/>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="4" t="inlineStr">
         <is>
-          <t>LatentView Analytics</t>
+          <t>LEAD School</t>
         </is>
       </c>
       <c r="B92" s="5" t="inlineStr">
         <is>
-          <t>https://www.latentview.com/careers/</t>
+          <t>https://leadschool.in/careers/</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
@@ -3656,31 +4044,35 @@
       </c>
       <c r="D92" s="4" t="inlineStr">
         <is>
-          <t>Analytics</t>
+          <t>EdTech</t>
         </is>
       </c>
       <c r="E92" s="4" t="inlineStr">
         <is>
-          <t>Chennai</t>
-        </is>
-      </c>
-      <c r="F92" s="4" t="inlineStr"/>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="F92" s="4" t="n">
+        <v/>
+      </c>
       <c r="G92" s="4" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H92" s="4" t="inlineStr"/>
+      <c r="H92" s="4" t="n">
+        <v/>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>LEAD School</t>
+          <t>LatentView Analytics</t>
         </is>
       </c>
       <c r="B93" s="5" t="inlineStr">
         <is>
-          <t>https://leadschool.in/careers/</t>
+          <t>https://www.latentview.com/careers/</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
@@ -3690,21 +4082,25 @@
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>EdTech</t>
+          <t>Analytics</t>
         </is>
       </c>
       <c r="E93" s="4" t="inlineStr">
         <is>
-          <t>Mumbai</t>
-        </is>
-      </c>
-      <c r="F93" s="4" t="inlineStr"/>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="F93" s="4" t="n">
+        <v/>
+      </c>
       <c r="G93" s="4" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H93" s="4" t="inlineStr"/>
+      <c r="H93" s="4" t="n">
+        <v/>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="4" t="inlineStr">
@@ -3732,13 +4128,17 @@
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="F94" s="4" t="inlineStr"/>
+      <c r="F94" s="4" t="n">
+        <v/>
+      </c>
       <c r="G94" s="4" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H94" s="4" t="inlineStr"/>
+      <c r="H94" s="4" t="n">
+        <v/>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="4" t="inlineStr">
@@ -3766,13 +4166,17 @@
           <t>Gurugram</t>
         </is>
       </c>
-      <c r="F95" s="4" t="inlineStr"/>
+      <c r="F95" s="4" t="n">
+        <v/>
+      </c>
       <c r="G95" s="4" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H95" s="4" t="inlineStr"/>
+      <c r="H95" s="4" t="n">
+        <v/>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="4" t="inlineStr">
@@ -3800,13 +4204,17 @@
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="F96" s="4" t="inlineStr"/>
+      <c r="F96" s="4" t="n">
+        <v/>
+      </c>
       <c r="G96" s="4" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H96" s="4" t="inlineStr"/>
+      <c r="H96" s="4" t="n">
+        <v/>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="4" t="inlineStr">
@@ -3834,13 +4242,17 @@
           <t>Chennai</t>
         </is>
       </c>
-      <c r="F97" s="4" t="inlineStr"/>
+      <c r="F97" s="4" t="n">
+        <v/>
+      </c>
       <c r="G97" s="4" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H97" s="4" t="inlineStr"/>
+      <c r="H97" s="4" t="n">
+        <v/>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="4" t="inlineStr">
@@ -3868,13 +4280,17 @@
           <t>Gurugram</t>
         </is>
       </c>
-      <c r="F98" s="4" t="inlineStr"/>
+      <c r="F98" s="4" t="n">
+        <v/>
+      </c>
       <c r="G98" s="4" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H98" s="4" t="inlineStr"/>
+      <c r="H98" s="4" t="n">
+        <v/>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="4" t="inlineStr">
@@ -3902,13 +4318,17 @@
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="F99" s="4" t="inlineStr"/>
+      <c r="F99" s="4" t="n">
+        <v/>
+      </c>
       <c r="G99" s="4" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H99" s="4" t="inlineStr"/>
+      <c r="H99" s="4" t="n">
+        <v/>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="4" t="inlineStr">
@@ -3918,7 +4338,7 @@
       </c>
       <c r="B100" s="5" t="inlineStr">
         <is>
-          <t>https://www.meesho.io/jobs</t>
+          <t>https://jobs.lever.co/meesho</t>
         </is>
       </c>
       <c r="C100" s="4" t="inlineStr">
@@ -3936,23 +4356,29 @@
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="F100" s="4" t="inlineStr"/>
+      <c r="F100" s="4" t="inlineStr">
+        <is>
+          <t>lever</t>
+        </is>
+      </c>
       <c r="G100" s="4" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H100" s="4" t="inlineStr"/>
+      <c r="H100" s="4" t="n">
+        <v/>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="4" t="inlineStr">
         <is>
-          <t>Mobile Premier League</t>
+          <t>MoEngage</t>
         </is>
       </c>
       <c r="B101" s="5" t="inlineStr">
         <is>
-          <t>https://www.mpl.live/careers</t>
+          <t>https://www.moengage.com/careers/</t>
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr">
@@ -3962,7 +4388,7 @@
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>Gaming</t>
+          <t>MarTech</t>
         </is>
       </c>
       <c r="E101" s="4" t="inlineStr">
@@ -3970,23 +4396,27 @@
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="F101" s="4" t="inlineStr"/>
+      <c r="F101" s="4" t="n">
+        <v/>
+      </c>
       <c r="G101" s="4" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H101" s="4" t="inlineStr"/>
+      <c r="H101" s="4" t="n">
+        <v/>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="4" t="inlineStr">
         <is>
-          <t>MoEngage</t>
+          <t>Mobile Premier League</t>
         </is>
       </c>
       <c r="B102" s="5" t="inlineStr">
         <is>
-          <t>https://www.moengage.com/careers/</t>
+          <t>https://www.mpl.live/careers</t>
         </is>
       </c>
       <c r="C102" s="4" t="inlineStr">
@@ -3996,7 +4426,7 @@
       </c>
       <c r="D102" s="4" t="inlineStr">
         <is>
-          <t>MarTech</t>
+          <t>Gaming</t>
         </is>
       </c>
       <c r="E102" s="4" t="inlineStr">
@@ -4004,13 +4434,17 @@
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="F102" s="4" t="inlineStr"/>
+      <c r="F102" s="4" t="n">
+        <v/>
+      </c>
       <c r="G102" s="4" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H102" s="4" t="inlineStr"/>
+      <c r="H102" s="4" t="n">
+        <v/>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="4" t="inlineStr">
@@ -4038,13 +4472,17 @@
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="F103" s="4" t="inlineStr"/>
+      <c r="F103" s="4" t="n">
+        <v/>
+      </c>
       <c r="G103" s="4" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H103" s="4" t="inlineStr"/>
+      <c r="H103" s="4" t="n">
+        <v/>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="4" t="inlineStr">
@@ -4072,13 +4510,17 @@
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="F104" s="4" t="inlineStr"/>
+      <c r="F104" s="4" t="n">
+        <v/>
+      </c>
       <c r="G104" s="4" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H104" s="4" t="inlineStr"/>
+      <c r="H104" s="4" t="n">
+        <v/>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="4" t="inlineStr">
@@ -4106,13 +4548,17 @@
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="F105" s="4" t="inlineStr"/>
+      <c r="F105" s="4" t="n">
+        <v/>
+      </c>
       <c r="G105" s="4" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H105" s="4" t="inlineStr"/>
+      <c r="H105" s="4" t="n">
+        <v/>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="4" t="inlineStr">
@@ -4122,7 +4568,7 @@
       </c>
       <c r="B106" s="5" t="inlineStr">
         <is>
-          <t>https://navi.com/careers</t>
+          <t>https://jobs.ashbyhq.com/navi</t>
         </is>
       </c>
       <c r="C106" s="4" t="inlineStr">
@@ -4140,13 +4586,19 @@
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="F106" s="4" t="inlineStr"/>
+      <c r="F106" s="4" t="inlineStr">
+        <is>
+          <t>ashby</t>
+        </is>
+      </c>
       <c r="G106" s="4" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H106" s="4" t="inlineStr"/>
+      <c r="H106" s="4" t="n">
+        <v/>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="4" t="inlineStr">
@@ -4174,13 +4626,17 @@
           <t>Mumbai</t>
         </is>
       </c>
-      <c r="F107" s="4" t="inlineStr"/>
+      <c r="F107" s="4" t="n">
+        <v/>
+      </c>
       <c r="G107" s="4" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H107" s="4" t="inlineStr"/>
+      <c r="H107" s="4" t="n">
+        <v/>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="4" t="inlineStr">
@@ -4208,13 +4664,17 @@
           <t>Mumbai</t>
         </is>
       </c>
-      <c r="F108" s="4" t="inlineStr"/>
+      <c r="F108" s="4" t="n">
+        <v/>
+      </c>
       <c r="G108" s="4" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H108" s="4" t="inlineStr"/>
+      <c r="H108" s="4" t="n">
+        <v/>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="4" t="inlineStr">
@@ -4242,13 +4702,17 @@
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="F109" s="4" t="inlineStr"/>
+      <c r="F109" s="4" t="n">
+        <v/>
+      </c>
       <c r="G109" s="4" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H109" s="4" t="inlineStr"/>
+      <c r="H109" s="4" t="n">
+        <v/>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="4" t="inlineStr">
@@ -4258,7 +4722,7 @@
       </c>
       <c r="B110" s="5" t="inlineStr">
         <is>
-          <t>https://www.nobroker.in/careers</t>
+          <t>https://careers.smartrecruiters.com/nobroker</t>
         </is>
       </c>
       <c r="C110" s="4" t="inlineStr">
@@ -4276,13 +4740,19 @@
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="F110" s="4" t="inlineStr"/>
+      <c r="F110" s="4" t="inlineStr">
+        <is>
+          <t>smartrecruiters</t>
+        </is>
+      </c>
       <c r="G110" s="4" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H110" s="4" t="inlineStr"/>
+      <c r="H110" s="4" t="n">
+        <v/>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="4" t="inlineStr">
@@ -4310,23 +4780,27 @@
           <t>Mumbai</t>
         </is>
       </c>
-      <c r="F111" s="4" t="inlineStr"/>
+      <c r="F111" s="4" t="n">
+        <v/>
+      </c>
       <c r="G111" s="4" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H111" s="4" t="inlineStr"/>
+      <c r="H111" s="4" t="n">
+        <v/>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="4" t="inlineStr">
         <is>
-          <t>Observe.AI</t>
+          <t>OYO</t>
         </is>
       </c>
       <c r="B112" s="5" t="inlineStr">
         <is>
-          <t>https://www.observe.ai/careers</t>
+          <t>https://www.oyorooms.com/careers/</t>
         </is>
       </c>
       <c r="C112" s="4" t="inlineStr">
@@ -4336,31 +4810,35 @@
       </c>
       <c r="D112" s="4" t="inlineStr">
         <is>
-          <t>AI SaaS</t>
+          <t>Hospitality</t>
         </is>
       </c>
       <c r="E112" s="4" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="F112" s="4" t="inlineStr"/>
+          <t>Gurugram</t>
+        </is>
+      </c>
+      <c r="F112" s="4" t="n">
+        <v/>
+      </c>
       <c r="G112" s="4" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H112" s="4" t="inlineStr"/>
+      <c r="H112" s="4" t="n">
+        <v/>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="4" t="inlineStr">
         <is>
-          <t>Ola</t>
+          <t>Observe.AI</t>
         </is>
       </c>
       <c r="B113" s="5" t="inlineStr">
         <is>
-          <t>https://www.olacabs.com/careers</t>
+          <t>https://www.observe.ai/careers</t>
         </is>
       </c>
       <c r="C113" s="4" t="inlineStr">
@@ -4370,7 +4848,7 @@
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>Mobility</t>
+          <t>AI SaaS</t>
         </is>
       </c>
       <c r="E113" s="4" t="inlineStr">
@@ -4378,23 +4856,27 @@
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="F113" s="4" t="inlineStr"/>
+      <c r="F113" s="4" t="n">
+        <v/>
+      </c>
       <c r="G113" s="4" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H113" s="4" t="inlineStr"/>
+      <c r="H113" s="4" t="n">
+        <v/>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="4" t="inlineStr">
         <is>
-          <t>Ola Electric</t>
+          <t>Ola</t>
         </is>
       </c>
       <c r="B114" s="5" t="inlineStr">
         <is>
-          <t>https://www.olaelectric.com/careers</t>
+          <t>https://www.olacabs.com/careers</t>
         </is>
       </c>
       <c r="C114" s="4" t="inlineStr">
@@ -4404,7 +4886,7 @@
       </c>
       <c r="D114" s="4" t="inlineStr">
         <is>
-          <t>EV</t>
+          <t>Mobility</t>
         </is>
       </c>
       <c r="E114" s="4" t="inlineStr">
@@ -4412,23 +4894,27 @@
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="F114" s="4" t="inlineStr"/>
+      <c r="F114" s="4" t="n">
+        <v/>
+      </c>
       <c r="G114" s="4" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H114" s="4" t="inlineStr"/>
+      <c r="H114" s="4" t="n">
+        <v/>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="4" t="inlineStr">
         <is>
-          <t>OYO</t>
+          <t>Ola Electric</t>
         </is>
       </c>
       <c r="B115" s="5" t="inlineStr">
         <is>
-          <t>https://www.oyorooms.com/careers/</t>
+          <t>https://www.olaelectric.com/careers</t>
         </is>
       </c>
       <c r="C115" s="4" t="inlineStr">
@@ -4438,21 +4924,25 @@
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>Hospitality</t>
+          <t>EV</t>
         </is>
       </c>
       <c r="E115" s="4" t="inlineStr">
         <is>
-          <t>Gurugram</t>
-        </is>
-      </c>
-      <c r="F115" s="4" t="inlineStr"/>
+          <t>Bengaluru</t>
+        </is>
+      </c>
+      <c r="F115" s="4" t="n">
+        <v/>
+      </c>
       <c r="G115" s="4" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H115" s="4" t="inlineStr"/>
+      <c r="H115" s="4" t="n">
+        <v/>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="4" t="inlineStr">
@@ -4462,7 +4952,7 @@
       </c>
       <c r="B116" s="5" t="inlineStr">
         <is>
-          <t>https://paytm.com/careers</t>
+          <t>https://jobs.lever.co/paytm</t>
         </is>
       </c>
       <c r="C116" s="4" t="inlineStr">
@@ -4480,13 +4970,19 @@
           <t>Noida</t>
         </is>
       </c>
-      <c r="F116" s="4" t="inlineStr"/>
+      <c r="F116" s="4" t="inlineStr">
+        <is>
+          <t>lever</t>
+        </is>
+      </c>
       <c r="G116" s="4" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H116" s="4" t="inlineStr"/>
+      <c r="H116" s="4" t="n">
+        <v/>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="4" t="inlineStr">
@@ -4514,13 +5010,17 @@
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="F117" s="4" t="inlineStr"/>
+      <c r="F117" s="4" t="n">
+        <v/>
+      </c>
       <c r="G117" s="4" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H117" s="4" t="inlineStr"/>
+      <c r="H117" s="4" t="n">
+        <v/>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="4" t="inlineStr">
@@ -4548,13 +5048,17 @@
           <t>Mumbai</t>
         </is>
       </c>
-      <c r="F118" s="4" t="inlineStr"/>
+      <c r="F118" s="4" t="n">
+        <v/>
+      </c>
       <c r="G118" s="4" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H118" s="4" t="inlineStr"/>
+      <c r="H118" s="4" t="n">
+        <v/>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="4" t="inlineStr">
@@ -4564,7 +5068,7 @@
       </c>
       <c r="B119" s="5" t="inlineStr">
         <is>
-          <t>https://www.phonepe.com/careers/job-openings/</t>
+          <t>https://boards.greenhouse.io/phonepe</t>
         </is>
       </c>
       <c r="C119" s="4" t="inlineStr">
@@ -4582,13 +5086,19 @@
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="F119" s="4" t="inlineStr"/>
+      <c r="F119" s="4" t="inlineStr">
+        <is>
+          <t>greenhouse</t>
+        </is>
+      </c>
       <c r="G119" s="4" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H119" s="4" t="inlineStr"/>
+      <c r="H119" s="4" t="n">
+        <v/>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="4" t="inlineStr">
@@ -4616,13 +5126,17 @@
           <t>Noida</t>
         </is>
       </c>
-      <c r="F120" s="4" t="inlineStr"/>
+      <c r="F120" s="4" t="n">
+        <v/>
+      </c>
       <c r="G120" s="4" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H120" s="4" t="inlineStr"/>
+      <c r="H120" s="4" t="n">
+        <v/>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="4" t="inlineStr">
@@ -4650,13 +5164,17 @@
           <t>Noida</t>
         </is>
       </c>
-      <c r="F121" s="4" t="inlineStr"/>
+      <c r="F121" s="4" t="n">
+        <v/>
+      </c>
       <c r="G121" s="4" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H121" s="4" t="inlineStr"/>
+      <c r="H121" s="4" t="n">
+        <v/>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="4" t="inlineStr">
@@ -4684,13 +5202,17 @@
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="F122" s="4" t="inlineStr"/>
+      <c r="F122" s="4" t="n">
+        <v/>
+      </c>
       <c r="G122" s="4" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H122" s="4" t="inlineStr"/>
+      <c r="H122" s="4" t="n">
+        <v/>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="4" t="inlineStr">
@@ -4700,7 +5222,7 @@
       </c>
       <c r="B123" s="5" t="inlineStr">
         <is>
-          <t>https://porter.in/careers</t>
+          <t>https://jobs.lever.co/porter</t>
         </is>
       </c>
       <c r="C123" s="4" t="inlineStr">
@@ -4718,13 +5240,19 @@
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="F123" s="4" t="inlineStr"/>
+      <c r="F123" s="4" t="inlineStr">
+        <is>
+          <t>lever</t>
+        </is>
+      </c>
       <c r="G123" s="4" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H123" s="4" t="inlineStr"/>
+      <c r="H123" s="4" t="n">
+        <v/>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="4" t="inlineStr">
@@ -4794,13 +5322,17 @@
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="F125" s="4" t="inlineStr"/>
+      <c r="F125" s="4" t="n">
+        <v/>
+      </c>
       <c r="G125" s="4" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H125" s="4" t="inlineStr"/>
+      <c r="H125" s="4" t="n">
+        <v/>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="4" t="inlineStr">
@@ -4828,13 +5360,17 @@
           <t>Gurugram</t>
         </is>
       </c>
-      <c r="F126" s="4" t="inlineStr"/>
+      <c r="F126" s="4" t="n">
+        <v/>
+      </c>
       <c r="G126" s="4" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H126" s="4" t="inlineStr"/>
+      <c r="H126" s="4" t="n">
+        <v/>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="4" t="inlineStr">
@@ -4862,13 +5398,17 @@
           <t>Mumbai</t>
         </is>
       </c>
-      <c r="F127" s="4" t="inlineStr"/>
+      <c r="F127" s="4" t="n">
+        <v/>
+      </c>
       <c r="G127" s="4" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H127" s="4" t="inlineStr"/>
+      <c r="H127" s="4" t="n">
+        <v/>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="4" t="inlineStr">
@@ -4896,13 +5436,17 @@
           <t>Mumbai</t>
         </is>
       </c>
-      <c r="F128" s="4" t="inlineStr"/>
+      <c r="F128" s="4" t="n">
+        <v/>
+      </c>
       <c r="G128" s="4" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H128" s="4" t="inlineStr"/>
+      <c r="H128" s="4" t="n">
+        <v/>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="4" t="inlineStr">
@@ -4930,13 +5474,17 @@
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="F129" s="4" t="inlineStr"/>
+      <c r="F129" s="4" t="n">
+        <v/>
+      </c>
       <c r="G129" s="4" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H129" s="4" t="inlineStr"/>
+      <c r="H129" s="4" t="n">
+        <v/>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="4" t="inlineStr">
@@ -4946,7 +5494,7 @@
       </c>
       <c r="B130" s="5" t="inlineStr">
         <is>
-          <t>https://razorpay.com/jobs/</t>
+          <t>https://boards.greenhouse.io/razorpaysoftwareprivatelimited</t>
         </is>
       </c>
       <c r="C130" s="4" t="inlineStr">
@@ -4964,13 +5512,19 @@
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="F130" s="4" t="inlineStr"/>
+      <c r="F130" s="4" t="inlineStr">
+        <is>
+          <t>greenhouse</t>
+        </is>
+      </c>
       <c r="G130" s="4" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H130" s="4" t="inlineStr"/>
+      <c r="H130" s="4" t="n">
+        <v/>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="4" t="inlineStr">
@@ -4998,13 +5552,17 @@
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="F131" s="4" t="inlineStr"/>
+      <c r="F131" s="4" t="n">
+        <v/>
+      </c>
       <c r="G131" s="4" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H131" s="4" t="inlineStr"/>
+      <c r="H131" s="4" t="n">
+        <v/>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="4" t="inlineStr">
@@ -5032,13 +5590,17 @@
           <t>Gurugram</t>
         </is>
       </c>
-      <c r="F132" s="4" t="inlineStr"/>
+      <c r="F132" s="4" t="n">
+        <v/>
+      </c>
       <c r="G132" s="4" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H132" s="4" t="inlineStr"/>
+      <c r="H132" s="4" t="n">
+        <v/>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="4" t="inlineStr">
@@ -5066,13 +5628,17 @@
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="F133" s="4" t="inlineStr"/>
+      <c r="F133" s="4" t="n">
+        <v/>
+      </c>
       <c r="G133" s="4" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H133" s="4" t="inlineStr"/>
+      <c r="H133" s="4" t="n">
+        <v/>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="4" t="inlineStr">
@@ -5100,13 +5666,17 @@
           <t>Gurugram</t>
         </is>
       </c>
-      <c r="F134" s="4" t="inlineStr"/>
+      <c r="F134" s="4" t="n">
+        <v/>
+      </c>
       <c r="G134" s="4" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H134" s="4" t="inlineStr"/>
+      <c r="H134" s="4" t="n">
+        <v/>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="4" t="inlineStr">
@@ -5134,13 +5704,17 @@
           <t>Gurugram</t>
         </is>
       </c>
-      <c r="F135" s="4" t="inlineStr"/>
+      <c r="F135" s="4" t="n">
+        <v/>
+      </c>
       <c r="G135" s="4" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H135" s="4" t="inlineStr"/>
+      <c r="H135" s="4" t="n">
+        <v/>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="4" t="inlineStr">
@@ -5168,13 +5742,17 @@
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="F136" s="4" t="inlineStr"/>
+      <c r="F136" s="4" t="n">
+        <v/>
+      </c>
       <c r="G136" s="4" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H136" s="4" t="inlineStr"/>
+      <c r="H136" s="4" t="n">
+        <v/>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="4" t="inlineStr">
@@ -5202,13 +5780,17 @@
           <t>Gurugram</t>
         </is>
       </c>
-      <c r="F137" s="4" t="inlineStr"/>
+      <c r="F137" s="4" t="n">
+        <v/>
+      </c>
       <c r="G137" s="4" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H137" s="4" t="inlineStr"/>
+      <c r="H137" s="4" t="n">
+        <v/>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="4" t="inlineStr">
@@ -5236,13 +5818,17 @@
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="F138" s="4" t="inlineStr"/>
+      <c r="F138" s="4" t="n">
+        <v/>
+      </c>
       <c r="G138" s="4" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H138" s="4" t="inlineStr"/>
+      <c r="H138" s="4" t="n">
+        <v/>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="4" t="inlineStr">
@@ -5270,13 +5856,17 @@
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="F139" s="4" t="inlineStr"/>
+      <c r="F139" s="4" t="n">
+        <v/>
+      </c>
       <c r="G139" s="4" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H139" s="4" t="inlineStr"/>
+      <c r="H139" s="4" t="n">
+        <v/>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="4" t="inlineStr">
@@ -5286,7 +5876,7 @@
       </c>
       <c r="B140" s="5" t="inlineStr">
         <is>
-          <t>https://unacademy.com/careers</t>
+          <t>https://careers.smartrecruiters.com/unacademy</t>
         </is>
       </c>
       <c r="C140" s="4" t="inlineStr">
@@ -5304,13 +5894,19 @@
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="F140" s="4" t="inlineStr"/>
+      <c r="F140" s="4" t="inlineStr">
+        <is>
+          <t>smartrecruiters</t>
+        </is>
+      </c>
       <c r="G140" s="4" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H140" s="4" t="inlineStr"/>
+      <c r="H140" s="4" t="n">
+        <v/>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="4" t="inlineStr">
@@ -5338,23 +5934,27 @@
           <t>Chennai</t>
         </is>
       </c>
-      <c r="F141" s="4" t="inlineStr"/>
+      <c r="F141" s="4" t="n">
+        <v/>
+      </c>
       <c r="G141" s="4" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H141" s="4" t="inlineStr"/>
+      <c r="H141" s="4" t="n">
+        <v/>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="4" t="inlineStr">
         <is>
-          <t>upGrad</t>
+          <t>Upstox</t>
         </is>
       </c>
       <c r="B142" s="5" t="inlineStr">
         <is>
-          <t>https://www.upgrad.com/careers/</t>
+          <t>https://careers.smartrecruiters.com/upstox</t>
         </is>
       </c>
       <c r="C142" s="4" t="inlineStr">
@@ -5364,7 +5964,7 @@
       </c>
       <c r="D142" s="4" t="inlineStr">
         <is>
-          <t>EdTech</t>
+          <t>Fintech</t>
         </is>
       </c>
       <c r="E142" s="4" t="inlineStr">
@@ -5372,23 +5972,29 @@
           <t>Mumbai</t>
         </is>
       </c>
-      <c r="F142" s="4" t="inlineStr"/>
+      <c r="F142" s="4" t="inlineStr">
+        <is>
+          <t>smartrecruiters</t>
+        </is>
+      </c>
       <c r="G142" s="4" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H142" s="4" t="inlineStr"/>
+      <c r="H142" s="4" t="n">
+        <v/>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="4" t="inlineStr">
         <is>
-          <t>Upstox</t>
+          <t>Urban Company</t>
         </is>
       </c>
       <c r="B143" s="5" t="inlineStr">
         <is>
-          <t>https://upstox.com/careers/</t>
+          <t>https://www.urbancompany.com/careers</t>
         </is>
       </c>
       <c r="C143" s="4" t="inlineStr">
@@ -5398,31 +6004,35 @@
       </c>
       <c r="D143" s="4" t="inlineStr">
         <is>
-          <t>Fintech</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="E143" s="4" t="inlineStr">
         <is>
-          <t>Mumbai</t>
-        </is>
-      </c>
-      <c r="F143" s="4" t="inlineStr"/>
+          <t>Gurugram</t>
+        </is>
+      </c>
+      <c r="F143" s="4" t="n">
+        <v/>
+      </c>
       <c r="G143" s="4" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H143" s="4" t="inlineStr"/>
+      <c r="H143" s="4" t="n">
+        <v/>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="4" t="inlineStr">
         <is>
-          <t>Urban Company</t>
+          <t>Vedantu</t>
         </is>
       </c>
       <c r="B144" s="5" t="inlineStr">
         <is>
-          <t>https://www.urbancompany.com/careers</t>
+          <t>https://www.vedantu.com/careers</t>
         </is>
       </c>
       <c r="C144" s="4" t="inlineStr">
@@ -5432,31 +6042,35 @@
       </c>
       <c r="D144" s="4" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>EdTech</t>
         </is>
       </c>
       <c r="E144" s="4" t="inlineStr">
         <is>
-          <t>Gurugram</t>
-        </is>
-      </c>
-      <c r="F144" s="4" t="inlineStr"/>
+          <t>Bengaluru</t>
+        </is>
+      </c>
+      <c r="F144" s="4" t="n">
+        <v/>
+      </c>
       <c r="G144" s="4" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H144" s="4" t="inlineStr"/>
+      <c r="H144" s="4" t="n">
+        <v/>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="4" t="inlineStr">
         <is>
-          <t>Vedantu</t>
+          <t>Whatfix</t>
         </is>
       </c>
       <c r="B145" s="5" t="inlineStr">
         <is>
-          <t>https://www.vedantu.com/careers</t>
+          <t>https://careers.smartrecruiters.com/whatfix</t>
         </is>
       </c>
       <c r="C145" s="4" t="inlineStr">
@@ -5466,7 +6080,7 @@
       </c>
       <c r="D145" s="4" t="inlineStr">
         <is>
-          <t>EdTech</t>
+          <t>SaaS</t>
         </is>
       </c>
       <c r="E145" s="4" t="inlineStr">
@@ -5474,23 +6088,29 @@
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="F145" s="4" t="inlineStr"/>
+      <c r="F145" s="4" t="inlineStr">
+        <is>
+          <t>smartrecruiters</t>
+        </is>
+      </c>
       <c r="G145" s="4" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H145" s="4" t="inlineStr"/>
+      <c r="H145" s="4" t="n">
+        <v/>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="4" t="inlineStr">
         <is>
-          <t>Whatfix</t>
+          <t>WinZO</t>
         </is>
       </c>
       <c r="B146" s="5" t="inlineStr">
         <is>
-          <t>https://whatfix.com/careers/</t>
+          <t>https://www.winzogames.com/careers</t>
         </is>
       </c>
       <c r="C146" s="4" t="inlineStr">
@@ -5500,31 +6120,35 @@
       </c>
       <c r="D146" s="4" t="inlineStr">
         <is>
-          <t>SaaS</t>
+          <t>Gaming</t>
         </is>
       </c>
       <c r="E146" s="4" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="F146" s="4" t="inlineStr"/>
+          <t>Delhi</t>
+        </is>
+      </c>
+      <c r="F146" s="4" t="n">
+        <v/>
+      </c>
       <c r="G146" s="4" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H146" s="4" t="inlineStr"/>
+      <c r="H146" s="4" t="n">
+        <v/>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="4" t="inlineStr">
         <is>
-          <t>WinZO</t>
+          <t>Yellow.ai</t>
         </is>
       </c>
       <c r="B147" s="5" t="inlineStr">
         <is>
-          <t>https://www.winzogames.com/careers</t>
+          <t>https://yellow.ai/careers/</t>
         </is>
       </c>
       <c r="C147" s="4" t="inlineStr">
@@ -5534,31 +6158,35 @@
       </c>
       <c r="D147" s="4" t="inlineStr">
         <is>
-          <t>Gaming</t>
+          <t>AI SaaS</t>
         </is>
       </c>
       <c r="E147" s="4" t="inlineStr">
         <is>
-          <t>Delhi</t>
-        </is>
-      </c>
-      <c r="F147" s="4" t="inlineStr"/>
+          <t>Bengaluru</t>
+        </is>
+      </c>
+      <c r="F147" s="4" t="n">
+        <v/>
+      </c>
       <c r="G147" s="4" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H147" s="4" t="inlineStr"/>
+      <c r="H147" s="4" t="n">
+        <v/>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="4" t="inlineStr">
         <is>
-          <t>Yellow.ai</t>
+          <t>Yubi</t>
         </is>
       </c>
       <c r="B148" s="5" t="inlineStr">
         <is>
-          <t>https://yellow.ai/careers/</t>
+          <t>https://www.go-yubi.com/careers/</t>
         </is>
       </c>
       <c r="C148" s="4" t="inlineStr">
@@ -5568,31 +6196,35 @@
       </c>
       <c r="D148" s="4" t="inlineStr">
         <is>
-          <t>AI SaaS</t>
+          <t>Fintech</t>
         </is>
       </c>
       <c r="E148" s="4" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="F148" s="4" t="inlineStr"/>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="F148" s="4" t="n">
+        <v/>
+      </c>
       <c r="G148" s="4" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H148" s="4" t="inlineStr"/>
+      <c r="H148" s="4" t="n">
+        <v/>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="4" t="inlineStr">
         <is>
-          <t>Yubi</t>
+          <t>Zenoti</t>
         </is>
       </c>
       <c r="B149" s="5" t="inlineStr">
         <is>
-          <t>https://www.go-yubi.com/careers/</t>
+          <t>https://boards.greenhouse.io/zenoti</t>
         </is>
       </c>
       <c r="C149" s="4" t="inlineStr">
@@ -5602,31 +6234,37 @@
       </c>
       <c r="D149" s="4" t="inlineStr">
         <is>
-          <t>Fintech</t>
+          <t>SaaS</t>
         </is>
       </c>
       <c r="E149" s="4" t="inlineStr">
         <is>
-          <t>Chennai</t>
-        </is>
-      </c>
-      <c r="F149" s="4" t="inlineStr"/>
+          <t>Hyderabad</t>
+        </is>
+      </c>
+      <c r="F149" s="4" t="inlineStr">
+        <is>
+          <t>greenhouse</t>
+        </is>
+      </c>
       <c r="G149" s="4" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H149" s="4" t="inlineStr"/>
+      <c r="H149" s="4" t="n">
+        <v/>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="4" t="inlineStr">
         <is>
-          <t>Zenoti</t>
+          <t>Zepto</t>
         </is>
       </c>
       <c r="B150" s="5" t="inlineStr">
         <is>
-          <t>https://www.zenoti.com/careers</t>
+          <t>https://www.zeptonow.com/careers</t>
         </is>
       </c>
       <c r="C150" s="4" t="inlineStr">
@@ -5636,31 +6274,35 @@
       </c>
       <c r="D150" s="4" t="inlineStr">
         <is>
-          <t>SaaS</t>
+          <t>Quick Commerce</t>
         </is>
       </c>
       <c r="E150" s="4" t="inlineStr">
         <is>
-          <t>Hyderabad</t>
-        </is>
-      </c>
-      <c r="F150" s="4" t="inlineStr"/>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="F150" s="4" t="n">
+        <v/>
+      </c>
       <c r="G150" s="4" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H150" s="4" t="inlineStr"/>
+      <c r="H150" s="4" t="n">
+        <v/>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="4" t="inlineStr">
         <is>
-          <t>Zepto</t>
+          <t>Zerodha</t>
         </is>
       </c>
       <c r="B151" s="5" t="inlineStr">
         <is>
-          <t>https://www.zeptonow.com/careers</t>
+          <t>https://zerodha.com/careers/</t>
         </is>
       </c>
       <c r="C151" s="4" t="inlineStr">
@@ -5670,31 +6312,35 @@
       </c>
       <c r="D151" s="4" t="inlineStr">
         <is>
-          <t>Quick Commerce</t>
+          <t>Fintech</t>
         </is>
       </c>
       <c r="E151" s="4" t="inlineStr">
         <is>
-          <t>Mumbai</t>
-        </is>
-      </c>
-      <c r="F151" s="4" t="inlineStr"/>
+          <t>Bengaluru</t>
+        </is>
+      </c>
+      <c r="F151" s="4" t="n">
+        <v/>
+      </c>
       <c r="G151" s="4" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H151" s="4" t="inlineStr"/>
+      <c r="H151" s="4" t="n">
+        <v/>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="4" t="inlineStr">
         <is>
-          <t>Zerodha</t>
+          <t>Zeta</t>
         </is>
       </c>
       <c r="B152" s="5" t="inlineStr">
         <is>
-          <t>https://zerodha.com/careers/</t>
+          <t>https://jobs.lever.co/zeta</t>
         </is>
       </c>
       <c r="C152" s="4" t="inlineStr">
@@ -5712,23 +6358,29 @@
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="F152" s="4" t="inlineStr"/>
+      <c r="F152" s="4" t="inlineStr">
+        <is>
+          <t>lever</t>
+        </is>
+      </c>
       <c r="G152" s="4" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H152" s="4" t="inlineStr"/>
+      <c r="H152" s="4" t="n">
+        <v/>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="4" t="inlineStr">
         <is>
-          <t>Zeta</t>
+          <t>Zetwerk</t>
         </is>
       </c>
       <c r="B153" s="5" t="inlineStr">
         <is>
-          <t>https://www.zeta.tech/careers</t>
+          <t>https://www.zetwerk.com/careers/</t>
         </is>
       </c>
       <c r="C153" s="4" t="inlineStr">
@@ -5738,7 +6390,7 @@
       </c>
       <c r="D153" s="4" t="inlineStr">
         <is>
-          <t>Fintech</t>
+          <t>Manufacturing</t>
         </is>
       </c>
       <c r="E153" s="4" t="inlineStr">
@@ -5746,23 +6398,27 @@
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="F153" s="4" t="inlineStr"/>
+      <c r="F153" s="4" t="n">
+        <v/>
+      </c>
       <c r="G153" s="4" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H153" s="4" t="inlineStr"/>
+      <c r="H153" s="4" t="n">
+        <v/>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="4" t="inlineStr">
         <is>
-          <t>Zetwerk</t>
+          <t>Zomato</t>
         </is>
       </c>
       <c r="B154" s="5" t="inlineStr">
         <is>
-          <t>https://www.zetwerk.com/careers/</t>
+          <t>https://www.zomato.com/careers</t>
         </is>
       </c>
       <c r="C154" s="4" t="inlineStr">
@@ -5772,31 +6428,35 @@
       </c>
       <c r="D154" s="4" t="inlineStr">
         <is>
-          <t>Manufacturing</t>
+          <t>Food Delivery</t>
         </is>
       </c>
       <c r="E154" s="4" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="F154" s="4" t="inlineStr"/>
+          <t>Gurugram</t>
+        </is>
+      </c>
+      <c r="F154" s="4" t="n">
+        <v/>
+      </c>
       <c r="G154" s="4" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H154" s="4" t="inlineStr"/>
+      <c r="H154" s="4" t="n">
+        <v/>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="4" t="inlineStr">
         <is>
-          <t>Zomato</t>
+          <t>Zupee</t>
         </is>
       </c>
       <c r="B155" s="5" t="inlineStr">
         <is>
-          <t>https://www.zomato.com/careers</t>
+          <t>https://www.zupee.com/careers/</t>
         </is>
       </c>
       <c r="C155" s="4" t="inlineStr">
@@ -5806,7 +6466,7 @@
       </c>
       <c r="D155" s="4" t="inlineStr">
         <is>
-          <t>Food Delivery</t>
+          <t>Gaming</t>
         </is>
       </c>
       <c r="E155" s="4" t="inlineStr">
@@ -5814,23 +6474,27 @@
           <t>Gurugram</t>
         </is>
       </c>
-      <c r="F155" s="4" t="inlineStr"/>
+      <c r="F155" s="4" t="n">
+        <v/>
+      </c>
       <c r="G155" s="4" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H155" s="4" t="inlineStr"/>
+      <c r="H155" s="4" t="n">
+        <v/>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="4" t="inlineStr">
         <is>
-          <t>Zupee</t>
+          <t>upGrad</t>
         </is>
       </c>
       <c r="B156" s="5" t="inlineStr">
         <is>
-          <t>https://www.zupee.com/careers/</t>
+          <t>https://www.upgrad.com/careers/</t>
         </is>
       </c>
       <c r="C156" s="4" t="inlineStr">
@@ -5840,31 +6504,35 @@
       </c>
       <c r="D156" s="4" t="inlineStr">
         <is>
-          <t>Gaming</t>
+          <t>EdTech</t>
         </is>
       </c>
       <c r="E156" s="4" t="inlineStr">
         <is>
-          <t>Gurugram</t>
-        </is>
-      </c>
-      <c r="F156" s="4" t="inlineStr"/>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="F156" s="4" t="n">
+        <v/>
+      </c>
       <c r="G156" s="4" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H156" s="4" t="inlineStr"/>
+      <c r="H156" s="4" t="n">
+        <v/>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="6" t="inlineStr">
         <is>
-          <t>Adobe India</t>
+          <t>AMD India</t>
         </is>
       </c>
       <c r="B157" s="7" t="inlineStr">
         <is>
-          <t>https://careers.adobe.com/us/en/search-results</t>
+          <t>https://careers.amd.com/</t>
         </is>
       </c>
       <c r="C157" s="6" t="inlineStr">
@@ -5874,31 +6542,37 @@
       </c>
       <c r="D157" s="6" t="inlineStr">
         <is>
-          <t>Big Tech</t>
+          <t>Semiconductor</t>
         </is>
       </c>
       <c r="E157" s="6" t="inlineStr">
         <is>
-          <t>Noida</t>
-        </is>
-      </c>
-      <c r="F157" s="6" t="inlineStr"/>
-      <c r="G157" s="6" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="H157" s="6" t="inlineStr"/>
+          <t>Bengaluru</t>
+        </is>
+      </c>
+      <c r="F157" s="6" t="n">
+        <v/>
+      </c>
+      <c r="G157" s="8" t="inlineStr">
+        <is>
+          <t>Inactive</t>
+        </is>
+      </c>
+      <c r="H157" s="6" t="inlineStr">
+        <is>
+          <t>Workday/Taleo portal - not supported by scraper, enable only if audit verifies</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="6" t="inlineStr">
         <is>
-          <t>Agoda India</t>
+          <t>Adobe India</t>
         </is>
       </c>
       <c r="B158" s="7" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/</t>
+          <t>https://careers.adobe.com/us/en/search-results</t>
         </is>
       </c>
       <c r="C158" s="6" t="inlineStr">
@@ -5908,31 +6582,35 @@
       </c>
       <c r="D158" s="6" t="inlineStr">
         <is>
-          <t>Travel</t>
+          <t>Big Tech</t>
         </is>
       </c>
       <c r="E158" s="6" t="inlineStr">
         <is>
-          <t>Gurugram</t>
-        </is>
-      </c>
-      <c r="F158" s="6" t="inlineStr"/>
+          <t>Noida</t>
+        </is>
+      </c>
+      <c r="F158" s="6" t="n">
+        <v/>
+      </c>
       <c r="G158" s="6" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H158" s="6" t="inlineStr"/>
+      <c r="H158" s="6" t="n">
+        <v/>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="6" t="inlineStr">
         <is>
-          <t>Airbus India</t>
+          <t>Agoda India</t>
         </is>
       </c>
       <c r="B159" s="7" t="inlineStr">
         <is>
-          <t>https://www.airbus.com/en/careers</t>
+          <t>https://careersatagoda.com/</t>
         </is>
       </c>
       <c r="C159" s="6" t="inlineStr">
@@ -5942,35 +6620,35 @@
       </c>
       <c r="D159" s="6" t="inlineStr">
         <is>
-          <t>Aerospace</t>
+          <t>Travel</t>
         </is>
       </c>
       <c r="E159" s="6" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="F159" s="6" t="inlineStr"/>
-      <c r="G159" s="8" t="inlineStr">
-        <is>
-          <t>Inactive</t>
-        </is>
-      </c>
-      <c r="H159" s="6" t="inlineStr">
-        <is>
-          <t>Workday/Taleo portal - not supported by scraper, enable only if audit verifies</t>
-        </is>
+          <t>Gurugram</t>
+        </is>
+      </c>
+      <c r="F159" s="6" t="n">
+        <v/>
+      </c>
+      <c r="G159" s="6" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="H159" s="6" t="n">
+        <v/>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="6" t="inlineStr">
         <is>
-          <t>Akamai India</t>
+          <t>Airbus India</t>
         </is>
       </c>
       <c r="B160" s="7" t="inlineStr">
         <is>
-          <t>https://akamaicareers.inflightcloud.com/search</t>
+          <t>https://www.airbus.com/en/careers</t>
         </is>
       </c>
       <c r="C160" s="6" t="inlineStr">
@@ -5980,7 +6658,7 @@
       </c>
       <c r="D160" s="6" t="inlineStr">
         <is>
-          <t>Infra</t>
+          <t>Aerospace</t>
         </is>
       </c>
       <c r="E160" s="6" t="inlineStr">
@@ -5988,23 +6666,29 @@
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="F160" s="6" t="inlineStr"/>
-      <c r="G160" s="6" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="H160" s="6" t="inlineStr"/>
+      <c r="F160" s="6" t="n">
+        <v/>
+      </c>
+      <c r="G160" s="8" t="inlineStr">
+        <is>
+          <t>Inactive</t>
+        </is>
+      </c>
+      <c r="H160" s="6" t="inlineStr">
+        <is>
+          <t>Workday/Taleo portal - not supported by scraper, enable only if audit verifies</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="6" t="inlineStr">
         <is>
-          <t>Amazon India</t>
+          <t>Akamai India</t>
         </is>
       </c>
       <c r="B161" s="7" t="inlineStr">
         <is>
-          <t>https://www.amazon.jobs/en/locations/india</t>
+          <t>https://akamaicareers.inflightcloud.com/search</t>
         </is>
       </c>
       <c r="C161" s="6" t="inlineStr">
@@ -6014,7 +6698,7 @@
       </c>
       <c r="D161" s="6" t="inlineStr">
         <is>
-          <t>Big Tech</t>
+          <t>Infra</t>
         </is>
       </c>
       <c r="E161" s="6" t="inlineStr">
@@ -6022,23 +6706,27 @@
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="F161" s="6" t="inlineStr"/>
+      <c r="F161" s="6" t="n">
+        <v/>
+      </c>
       <c r="G161" s="6" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H161" s="6" t="inlineStr"/>
+      <c r="H161" s="6" t="n">
+        <v/>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="6" t="inlineStr">
         <is>
-          <t>AMD India</t>
+          <t>Amazon India</t>
         </is>
       </c>
       <c r="B162" s="7" t="inlineStr">
         <is>
-          <t>https://careers.amd.com/</t>
+          <t>https://www.amazon.jobs/en/locations/india</t>
         </is>
       </c>
       <c r="C162" s="6" t="inlineStr">
@@ -6048,7 +6736,7 @@
       </c>
       <c r="D162" s="6" t="inlineStr">
         <is>
-          <t>Semiconductor</t>
+          <t>Big Tech</t>
         </is>
       </c>
       <c r="E162" s="6" t="inlineStr">
@@ -6056,16 +6744,16 @@
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="F162" s="6" t="inlineStr"/>
-      <c r="G162" s="8" t="inlineStr">
-        <is>
-          <t>Inactive</t>
-        </is>
-      </c>
-      <c r="H162" s="6" t="inlineStr">
-        <is>
-          <t>Workday/Taleo portal - not supported by scraper, enable only if audit verifies</t>
-        </is>
+      <c r="F162" s="6" t="n">
+        <v/>
+      </c>
+      <c r="G162" s="6" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="H162" s="6" t="n">
+        <v/>
       </c>
     </row>
     <row r="163">
@@ -6094,7 +6782,9 @@
           <t>Gurugram</t>
         </is>
       </c>
-      <c r="F163" s="6" t="inlineStr"/>
+      <c r="F163" s="6" t="n">
+        <v/>
+      </c>
       <c r="G163" s="8" t="inlineStr">
         <is>
           <t>Inactive</t>
@@ -6132,13 +6822,17 @@
           <t>Pune</t>
         </is>
       </c>
-      <c r="F164" s="6" t="inlineStr"/>
+      <c r="F164" s="6" t="n">
+        <v/>
+      </c>
       <c r="G164" s="6" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H164" s="6" t="inlineStr"/>
+      <c r="H164" s="6" t="n">
+        <v/>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="6" t="inlineStr">
@@ -6166,13 +6860,17 @@
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="F165" s="6" t="inlineStr"/>
+      <c r="F165" s="6" t="n">
+        <v/>
+      </c>
       <c r="G165" s="6" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H165" s="6" t="inlineStr"/>
+      <c r="H165" s="6" t="n">
+        <v/>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="6" t="inlineStr">
@@ -6200,13 +6898,17 @@
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="F166" s="6" t="inlineStr"/>
+      <c r="F166" s="6" t="n">
+        <v/>
+      </c>
       <c r="G166" s="6" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H166" s="6" t="inlineStr"/>
+      <c r="H166" s="6" t="n">
+        <v/>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="6" t="inlineStr">
@@ -6234,13 +6936,17 @@
           <t>Pune</t>
         </is>
       </c>
-      <c r="F167" s="6" t="inlineStr"/>
+      <c r="F167" s="6" t="n">
+        <v/>
+      </c>
       <c r="G167" s="6" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H167" s="6" t="inlineStr"/>
+      <c r="H167" s="6" t="n">
+        <v/>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="6" t="inlineStr">
@@ -6268,7 +6974,9 @@
           <t>Pune</t>
         </is>
       </c>
-      <c r="F168" s="6" t="inlineStr"/>
+      <c r="F168" s="6" t="n">
+        <v/>
+      </c>
       <c r="G168" s="8" t="inlineStr">
         <is>
           <t>Inactive</t>
@@ -6306,7 +7014,9 @@
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="F169" s="6" t="inlineStr"/>
+      <c r="F169" s="6" t="n">
+        <v/>
+      </c>
       <c r="G169" s="8" t="inlineStr">
         <is>
           <t>Inactive</t>
@@ -6326,7 +7036,7 @@
       </c>
       <c r="B170" s="7" t="inlineStr">
         <is>
-          <t>https://jobs.booking.com/careers</t>
+          <t>https://jobs.recruitee.com</t>
         </is>
       </c>
       <c r="C170" s="6" t="inlineStr">
@@ -6344,13 +7054,19 @@
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="F170" s="6" t="inlineStr"/>
+      <c r="F170" s="6" t="inlineStr">
+        <is>
+          <t>recruitee</t>
+        </is>
+      </c>
       <c r="G170" s="6" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H170" s="6" t="inlineStr"/>
+      <c r="H170" s="6" t="n">
+        <v/>
+      </c>
     </row>
     <row r="171">
       <c r="A171" s="6" t="inlineStr">
@@ -6378,7 +7094,9 @@
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="F171" s="6" t="inlineStr"/>
+      <c r="F171" s="6" t="n">
+        <v/>
+      </c>
       <c r="G171" s="8" t="inlineStr">
         <is>
           <t>Inactive</t>
@@ -6416,7 +7134,9 @@
           <t>Noida</t>
         </is>
       </c>
-      <c r="F172" s="6" t="inlineStr"/>
+      <c r="F172" s="6" t="n">
+        <v/>
+      </c>
       <c r="G172" s="8" t="inlineStr">
         <is>
           <t>Inactive</t>
@@ -6454,7 +7174,9 @@
           <t>Chennai</t>
         </is>
       </c>
-      <c r="F173" s="6" t="inlineStr"/>
+      <c r="F173" s="6" t="n">
+        <v/>
+      </c>
       <c r="G173" s="8" t="inlineStr">
         <is>
           <t>Inactive</t>
@@ -6474,7 +7196,7 @@
       </c>
       <c r="B174" s="7" t="inlineStr">
         <is>
-          <t>https://jobs.cisco.com/</t>
+          <t>https://jobs.recruitee.com</t>
         </is>
       </c>
       <c r="C174" s="6" t="inlineStr">
@@ -6492,13 +7214,19 @@
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="F174" s="6" t="inlineStr"/>
+      <c r="F174" s="6" t="inlineStr">
+        <is>
+          <t>recruitee</t>
+        </is>
+      </c>
       <c r="G174" s="6" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H174" s="6" t="inlineStr"/>
+      <c r="H174" s="6" t="n">
+        <v/>
+      </c>
     </row>
     <row r="175">
       <c r="A175" s="6" t="inlineStr">
@@ -6508,7 +7236,7 @@
       </c>
       <c r="B175" s="7" t="inlineStr">
         <is>
-          <t>https://www.cloudflare.com/careers/jobs/</t>
+          <t>https://boards.greenhouse.io/cloudflare</t>
         </is>
       </c>
       <c r="C175" s="6" t="inlineStr">
@@ -6526,13 +7254,19 @@
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="F175" s="6" t="inlineStr"/>
+      <c r="F175" s="6" t="inlineStr">
+        <is>
+          <t>greenhouse</t>
+        </is>
+      </c>
       <c r="G175" s="6" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H175" s="6" t="inlineStr"/>
+      <c r="H175" s="6" t="n">
+        <v/>
+      </c>
     </row>
     <row r="176">
       <c r="A176" s="6" t="inlineStr">
@@ -6560,13 +7294,17 @@
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="F176" s="6" t="inlineStr"/>
+      <c r="F176" s="6" t="n">
+        <v/>
+      </c>
       <c r="G176" s="6" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H176" s="6" t="inlineStr"/>
+      <c r="H176" s="6" t="n">
+        <v/>
+      </c>
     </row>
     <row r="177">
       <c r="A177" s="6" t="inlineStr">
@@ -6576,7 +7314,7 @@
       </c>
       <c r="B177" s="7" t="inlineStr">
         <is>
-          <t>https://www.commvault.com/careers</t>
+          <t>https://boards.greenhouse.io/commvault</t>
         </is>
       </c>
       <c r="C177" s="6" t="inlineStr">
@@ -6594,13 +7332,19 @@
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="F177" s="6" t="inlineStr"/>
+      <c r="F177" s="6" t="inlineStr">
+        <is>
+          <t>greenhouse</t>
+        </is>
+      </c>
       <c r="G177" s="6" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H177" s="6" t="inlineStr"/>
+      <c r="H177" s="6" t="n">
+        <v/>
+      </c>
     </row>
     <row r="178">
       <c r="A178" s="6" t="inlineStr">
@@ -6628,23 +7372,27 @@
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="F178" s="6" t="inlineStr"/>
+      <c r="F178" s="6" t="n">
+        <v/>
+      </c>
       <c r="G178" s="6" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H178" s="6" t="inlineStr"/>
+      <c r="H178" s="6" t="n">
+        <v/>
+      </c>
     </row>
     <row r="179">
-      <c r="A179" s="6" t="inlineStr">
+      <c r="A179" s="9" t="inlineStr">
         <is>
           <t>Continental India</t>
         </is>
       </c>
       <c r="B179" s="7" t="inlineStr">
         <is>
-          <t>https://www.continental.com/en/career/</t>
+          <t>https://careers.smartrecruiters.com/continental</t>
         </is>
       </c>
       <c r="C179" s="6" t="inlineStr">
@@ -6662,15 +7410,19 @@
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="F179" s="6" t="inlineStr"/>
-      <c r="G179" s="8" t="inlineStr">
-        <is>
-          <t>Inactive</t>
+      <c r="F179" s="6" t="inlineStr">
+        <is>
+          <t>smartrecruiters</t>
+        </is>
+      </c>
+      <c r="G179" s="6" t="inlineStr">
+        <is>
+          <t>Active</t>
         </is>
       </c>
       <c r="H179" s="6" t="inlineStr">
         <is>
-          <t>Workday/Taleo portal - not supported by scraper, enable only if audit verifies</t>
+          <t>Workday/Taleo portal - not supported by scraper, enable only if audit verifies | Auto-verified token, worth a quick manual sanity check.</t>
         </is>
       </c>
     </row>
@@ -6700,13 +7452,17 @@
           <t>Pune</t>
         </is>
       </c>
-      <c r="F180" s="6" t="inlineStr"/>
+      <c r="F180" s="6" t="n">
+        <v/>
+      </c>
       <c r="G180" s="6" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H180" s="6" t="inlineStr"/>
+      <c r="H180" s="6" t="n">
+        <v/>
+      </c>
     </row>
     <row r="181">
       <c r="A181" s="6" t="inlineStr">
@@ -6716,7 +7472,7 @@
       </c>
       <c r="B181" s="7" t="inlineStr">
         <is>
-          <t>https://www.databricks.com/company/careers/open-positions</t>
+          <t>https://boards.greenhouse.io/databricks</t>
         </is>
       </c>
       <c r="C181" s="6" t="inlineStr">
@@ -6734,13 +7490,19 @@
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="F181" s="6" t="inlineStr"/>
+      <c r="F181" s="6" t="inlineStr">
+        <is>
+          <t>greenhouse</t>
+        </is>
+      </c>
       <c r="G181" s="6" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H181" s="6" t="inlineStr"/>
+      <c r="H181" s="6" t="n">
+        <v/>
+      </c>
     </row>
     <row r="182">
       <c r="A182" s="6" t="inlineStr">
@@ -6768,7 +7530,9 @@
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="F182" s="6" t="inlineStr"/>
+      <c r="F182" s="6" t="n">
+        <v/>
+      </c>
       <c r="G182" s="8" t="inlineStr">
         <is>
           <t>Inactive</t>
@@ -6806,7 +7570,9 @@
           <t>Pune</t>
         </is>
       </c>
-      <c r="F183" s="6" t="inlineStr"/>
+      <c r="F183" s="6" t="n">
+        <v/>
+      </c>
       <c r="G183" s="8" t="inlineStr">
         <is>
           <t>Inactive</t>
@@ -6826,7 +7592,7 @@
       </c>
       <c r="B184" s="7" t="inlineStr">
         <is>
-          <t>https://jobs.elastic.co/jobs</t>
+          <t>https://jobs.recruitee.com</t>
         </is>
       </c>
       <c r="C184" s="6" t="inlineStr">
@@ -6844,13 +7610,19 @@
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="F184" s="6" t="inlineStr"/>
+      <c r="F184" s="6" t="inlineStr">
+        <is>
+          <t>recruitee</t>
+        </is>
+      </c>
       <c r="G184" s="6" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H184" s="6" t="inlineStr"/>
+      <c r="H184" s="6" t="n">
+        <v/>
+      </c>
     </row>
     <row r="185">
       <c r="A185" s="6" t="inlineStr">
@@ -6878,7 +7650,9 @@
           <t>Gurugram</t>
         </is>
       </c>
-      <c r="F185" s="6" t="inlineStr"/>
+      <c r="F185" s="6" t="n">
+        <v/>
+      </c>
       <c r="G185" s="8" t="inlineStr">
         <is>
           <t>Inactive</t>
@@ -6916,13 +7690,17 @@
           <t>Gurugram</t>
         </is>
       </c>
-      <c r="F186" s="6" t="inlineStr"/>
+      <c r="F186" s="6" t="n">
+        <v/>
+      </c>
       <c r="G186" s="6" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H186" s="6" t="inlineStr"/>
+      <c r="H186" s="6" t="n">
+        <v/>
+      </c>
     </row>
     <row r="187">
       <c r="A187" s="6" t="inlineStr">
@@ -6950,13 +7728,17 @@
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="F187" s="6" t="inlineStr"/>
+      <c r="F187" s="6" t="n">
+        <v/>
+      </c>
       <c r="G187" s="6" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H187" s="6" t="inlineStr"/>
+      <c r="H187" s="6" t="n">
+        <v/>
+      </c>
     </row>
     <row r="188">
       <c r="A188" s="6" t="inlineStr">
@@ -6966,7 +7748,7 @@
       </c>
       <c r="B188" s="7" t="inlineStr">
         <is>
-          <t>https://www.freshworks.com/company/careers/</t>
+          <t>https://careers.smartrecruiters.com/Freshworks</t>
         </is>
       </c>
       <c r="C188" s="6" t="inlineStr">
@@ -6984,13 +7766,19 @@
           <t>Chennai</t>
         </is>
       </c>
-      <c r="F188" s="6" t="inlineStr"/>
+      <c r="F188" s="6" t="inlineStr">
+        <is>
+          <t>smartrecruiters</t>
+        </is>
+      </c>
       <c r="G188" s="6" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H188" s="6" t="inlineStr"/>
+      <c r="H188" s="6" t="n">
+        <v/>
+      </c>
     </row>
     <row r="189">
       <c r="A189" s="6" t="inlineStr">
@@ -7018,7 +7806,9 @@
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="F189" s="6" t="inlineStr"/>
+      <c r="F189" s="6" t="n">
+        <v/>
+      </c>
       <c r="G189" s="8" t="inlineStr">
         <is>
           <t>Inactive</t>
@@ -7056,13 +7846,17 @@
           <t>Remote</t>
         </is>
       </c>
-      <c r="F190" s="6" t="inlineStr"/>
+      <c r="F190" s="6" t="n">
+        <v/>
+      </c>
       <c r="G190" s="6" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H190" s="6" t="inlineStr"/>
+      <c r="H190" s="6" t="n">
+        <v/>
+      </c>
     </row>
     <row r="191">
       <c r="A191" s="6" t="inlineStr">
@@ -7090,13 +7884,17 @@
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="F191" s="6" t="inlineStr"/>
+      <c r="F191" s="6" t="n">
+        <v/>
+      </c>
       <c r="G191" s="6" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H191" s="6" t="inlineStr"/>
+      <c r="H191" s="6" t="n">
+        <v/>
+      </c>
     </row>
     <row r="192">
       <c r="A192" s="6" t="inlineStr">
@@ -7106,7 +7904,7 @@
       </c>
       <c r="B192" s="7" t="inlineStr">
         <is>
-          <t>https://www.google.com/about/careers/applications/</t>
+          <t>https://google.recruitee.com</t>
         </is>
       </c>
       <c r="C192" s="6" t="inlineStr">
@@ -7124,23 +7922,29 @@
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="F192" s="6" t="inlineStr"/>
+      <c r="F192" s="6" t="inlineStr">
+        <is>
+          <t>recruitee</t>
+        </is>
+      </c>
       <c r="G192" s="6" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H192" s="6" t="inlineStr"/>
+      <c r="H192" s="6" t="n">
+        <v/>
+      </c>
     </row>
     <row r="193">
       <c r="A193" s="6" t="inlineStr">
         <is>
-          <t>Honeywell India</t>
+          <t>HP India</t>
         </is>
       </c>
       <c r="B193" s="7" t="inlineStr">
         <is>
-          <t>https://careers.honeywell.com/us/en</t>
+          <t>https://jobs.hp.com/</t>
         </is>
       </c>
       <c r="C193" s="6" t="inlineStr">
@@ -7150,7 +7954,7 @@
       </c>
       <c r="D193" s="6" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Hardware</t>
         </is>
       </c>
       <c r="E193" s="6" t="inlineStr">
@@ -7158,7 +7962,9 @@
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="F193" s="6" t="inlineStr"/>
+      <c r="F193" s="6" t="n">
+        <v/>
+      </c>
       <c r="G193" s="8" t="inlineStr">
         <is>
           <t>Inactive</t>
@@ -7173,12 +7979,12 @@
     <row r="194">
       <c r="A194" s="6" t="inlineStr">
         <is>
-          <t>HP India</t>
+          <t>HPE India</t>
         </is>
       </c>
       <c r="B194" s="7" t="inlineStr">
         <is>
-          <t>https://jobs.hp.com/</t>
+          <t>https://careers.hpe.com/</t>
         </is>
       </c>
       <c r="C194" s="6" t="inlineStr">
@@ -7196,7 +8002,9 @@
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="F194" s="6" t="inlineStr"/>
+      <c r="F194" s="6" t="n">
+        <v/>
+      </c>
       <c r="G194" s="8" t="inlineStr">
         <is>
           <t>Inactive</t>
@@ -7211,12 +8019,12 @@
     <row r="195">
       <c r="A195" s="6" t="inlineStr">
         <is>
-          <t>HPE India</t>
+          <t>HSBC Technology India</t>
         </is>
       </c>
       <c r="B195" s="7" t="inlineStr">
         <is>
-          <t>https://careers.hpe.com/</t>
+          <t>https://www.hsbc.com/careers</t>
         </is>
       </c>
       <c r="C195" s="6" t="inlineStr">
@@ -7226,15 +8034,17 @@
       </c>
       <c r="D195" s="6" t="inlineStr">
         <is>
-          <t>Hardware</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="E195" s="6" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="F195" s="6" t="inlineStr"/>
+          <t>Pune</t>
+        </is>
+      </c>
+      <c r="F195" s="6" t="n">
+        <v/>
+      </c>
       <c r="G195" s="8" t="inlineStr">
         <is>
           <t>Inactive</t>
@@ -7249,12 +8059,12 @@
     <row r="196">
       <c r="A196" s="6" t="inlineStr">
         <is>
-          <t>HSBC Technology India</t>
+          <t>Honeywell India</t>
         </is>
       </c>
       <c r="B196" s="7" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers</t>
+          <t>https://careers.honeywell.com/us/en</t>
         </is>
       </c>
       <c r="C196" s="6" t="inlineStr">
@@ -7264,15 +8074,17 @@
       </c>
       <c r="D196" s="6" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Industrial</t>
         </is>
       </c>
       <c r="E196" s="6" t="inlineStr">
         <is>
-          <t>Pune</t>
-        </is>
-      </c>
-      <c r="F196" s="6" t="inlineStr"/>
+          <t>Bengaluru</t>
+        </is>
+      </c>
+      <c r="F196" s="6" t="n">
+        <v/>
+      </c>
       <c r="G196" s="8" t="inlineStr">
         <is>
           <t>Inactive</t>
@@ -7310,7 +8122,9 @@
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="F197" s="6" t="inlineStr"/>
+      <c r="F197" s="6" t="n">
+        <v/>
+      </c>
       <c r="G197" s="8" t="inlineStr">
         <is>
           <t>Inactive</t>
@@ -7348,7 +8162,9 @@
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="F198" s="6" t="inlineStr"/>
+      <c r="F198" s="6" t="n">
+        <v/>
+      </c>
       <c r="G198" s="8" t="inlineStr">
         <is>
           <t>Inactive</t>
@@ -7386,7 +8202,9 @@
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="F199" s="6" t="inlineStr"/>
+      <c r="F199" s="6" t="n">
+        <v/>
+      </c>
       <c r="G199" s="8" t="inlineStr">
         <is>
           <t>Inactive</t>
@@ -7401,12 +8219,12 @@
     <row r="200">
       <c r="A200" s="6" t="inlineStr">
         <is>
-          <t>John Deere India</t>
+          <t>JPMorgan Chase India</t>
         </is>
       </c>
       <c r="B200" s="7" t="inlineStr">
         <is>
-          <t>https://careers.deere.com/</t>
+          <t>https://careers.jpmorgan.com/</t>
         </is>
       </c>
       <c r="C200" s="6" t="inlineStr">
@@ -7416,15 +8234,17 @@
       </c>
       <c r="D200" s="6" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="E200" s="6" t="inlineStr">
         <is>
-          <t>Pune</t>
-        </is>
-      </c>
-      <c r="F200" s="6" t="inlineStr"/>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="F200" s="6" t="n">
+        <v/>
+      </c>
       <c r="G200" s="8" t="inlineStr">
         <is>
           <t>Inactive</t>
@@ -7439,12 +8259,12 @@
     <row r="201">
       <c r="A201" s="6" t="inlineStr">
         <is>
-          <t>JPMorgan Chase India</t>
+          <t>John Deere India</t>
         </is>
       </c>
       <c r="B201" s="7" t="inlineStr">
         <is>
-          <t>https://careers.jpmorgan.com/</t>
+          <t>https://careers.deere.com/</t>
         </is>
       </c>
       <c r="C201" s="6" t="inlineStr">
@@ -7454,15 +8274,17 @@
       </c>
       <c r="D201" s="6" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Industrial</t>
         </is>
       </c>
       <c r="E201" s="6" t="inlineStr">
         <is>
-          <t>Mumbai</t>
-        </is>
-      </c>
-      <c r="F201" s="6" t="inlineStr"/>
+          <t>Pune</t>
+        </is>
+      </c>
+      <c r="F201" s="6" t="n">
+        <v/>
+      </c>
       <c r="G201" s="8" t="inlineStr">
         <is>
           <t>Inactive</t>
@@ -7500,7 +8322,9 @@
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="F202" s="6" t="inlineStr"/>
+      <c r="F202" s="6" t="n">
+        <v/>
+      </c>
       <c r="G202" s="8" t="inlineStr">
         <is>
           <t>Inactive</t>
@@ -7538,13 +8362,17 @@
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="F203" s="6" t="inlineStr"/>
+      <c r="F203" s="6" t="n">
+        <v/>
+      </c>
       <c r="G203" s="6" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H203" s="6" t="inlineStr"/>
+      <c r="H203" s="6" t="n">
+        <v/>
+      </c>
     </row>
     <row r="204">
       <c r="A204" s="6" t="inlineStr">
@@ -7572,7 +8400,9 @@
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="F204" s="6" t="inlineStr"/>
+      <c r="F204" s="6" t="n">
+        <v/>
+      </c>
       <c r="G204" s="8" t="inlineStr">
         <is>
           <t>Inactive</t>
@@ -7610,7 +8440,9 @@
           <t>Pune</t>
         </is>
       </c>
-      <c r="F205" s="6" t="inlineStr"/>
+      <c r="F205" s="6" t="n">
+        <v/>
+      </c>
       <c r="G205" s="8" t="inlineStr">
         <is>
           <t>Inactive</t>
@@ -7648,13 +8480,17 @@
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="F206" s="6" t="inlineStr"/>
+      <c r="F206" s="6" t="n">
+        <v/>
+      </c>
       <c r="G206" s="6" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H206" s="6" t="inlineStr"/>
+      <c r="H206" s="6" t="n">
+        <v/>
+      </c>
     </row>
     <row r="207">
       <c r="A207" s="6" t="inlineStr">
@@ -7682,7 +8518,9 @@
           <t>Hyderabad</t>
         </is>
       </c>
-      <c r="F207" s="6" t="inlineStr"/>
+      <c r="F207" s="6" t="n">
+        <v/>
+      </c>
       <c r="G207" s="8" t="inlineStr">
         <is>
           <t>Inactive</t>
@@ -7702,7 +8540,7 @@
       </c>
       <c r="B208" s="7" t="inlineStr">
         <is>
-          <t>https://jobs.careers.microsoft.com/global/en/search</t>
+          <t>https://jobs.recruitee.com</t>
         </is>
       </c>
       <c r="C208" s="6" t="inlineStr">
@@ -7720,13 +8558,19 @@
           <t>Hyderabad</t>
         </is>
       </c>
-      <c r="F208" s="6" t="inlineStr"/>
+      <c r="F208" s="6" t="inlineStr">
+        <is>
+          <t>recruitee</t>
+        </is>
+      </c>
       <c r="G208" s="6" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H208" s="6" t="inlineStr"/>
+      <c r="H208" s="6" t="n">
+        <v/>
+      </c>
     </row>
     <row r="209">
       <c r="A209" s="6" t="inlineStr">
@@ -7736,7 +8580,7 @@
       </c>
       <c r="B209" s="7" t="inlineStr">
         <is>
-          <t>https://www.mongodb.com/careers</t>
+          <t>https://boards.greenhouse.io/mongodb</t>
         </is>
       </c>
       <c r="C209" s="6" t="inlineStr">
@@ -7754,13 +8598,19 @@
           <t>Gurugram</t>
         </is>
       </c>
-      <c r="F209" s="6" t="inlineStr"/>
+      <c r="F209" s="6" t="inlineStr">
+        <is>
+          <t>greenhouse</t>
+        </is>
+      </c>
       <c r="G209" s="6" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H209" s="6" t="inlineStr"/>
+      <c r="H209" s="6" t="n">
+        <v/>
+      </c>
     </row>
     <row r="210">
       <c r="A210" s="6" t="inlineStr">
@@ -7788,7 +8638,9 @@
           <t>Mumbai</t>
         </is>
       </c>
-      <c r="F210" s="6" t="inlineStr"/>
+      <c r="F210" s="6" t="n">
+        <v/>
+      </c>
       <c r="G210" s="8" t="inlineStr">
         <is>
           <t>Inactive</t>
@@ -7826,7 +8678,9 @@
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="F211" s="6" t="inlineStr"/>
+      <c r="F211" s="6" t="n">
+        <v/>
+      </c>
       <c r="G211" s="8" t="inlineStr">
         <is>
           <t>Inactive</t>
@@ -7864,7 +8718,9 @@
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="F212" s="6" t="inlineStr"/>
+      <c r="F212" s="6" t="n">
+        <v/>
+      </c>
       <c r="G212" s="8" t="inlineStr">
         <is>
           <t>Inactive</t>
@@ -7902,13 +8758,17 @@
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="F213" s="6" t="inlineStr"/>
+      <c r="F213" s="6" t="n">
+        <v/>
+      </c>
       <c r="G213" s="6" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H213" s="6" t="inlineStr"/>
+      <c r="H213" s="6" t="n">
+        <v/>
+      </c>
     </row>
     <row r="214">
       <c r="A214" s="6" t="inlineStr">
@@ -7936,7 +8796,9 @@
           <t>Pune</t>
         </is>
       </c>
-      <c r="F214" s="6" t="inlineStr"/>
+      <c r="F214" s="6" t="n">
+        <v/>
+      </c>
       <c r="G214" s="8" t="inlineStr">
         <is>
           <t>Inactive</t>
@@ -7956,7 +8818,7 @@
       </c>
       <c r="B215" s="7" t="inlineStr">
         <is>
-          <t>https://www.okta.com/company/careers/</t>
+          <t>https://boards.greenhouse.io/okta</t>
         </is>
       </c>
       <c r="C215" s="6" t="inlineStr">
@@ -7974,13 +8836,19 @@
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="F215" s="6" t="inlineStr"/>
+      <c r="F215" s="6" t="inlineStr">
+        <is>
+          <t>greenhouse</t>
+        </is>
+      </c>
       <c r="G215" s="6" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H215" s="6" t="inlineStr"/>
+      <c r="H215" s="6" t="n">
+        <v/>
+      </c>
     </row>
     <row r="216">
       <c r="A216" s="6" t="inlineStr">
@@ -8008,7 +8876,9 @@
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="F216" s="6" t="inlineStr"/>
+      <c r="F216" s="6" t="n">
+        <v/>
+      </c>
       <c r="G216" s="8" t="inlineStr">
         <is>
           <t>Inactive</t>
@@ -8023,12 +8893,12 @@
     <row r="217">
       <c r="A217" s="6" t="inlineStr">
         <is>
-          <t>Palo Alto Networks India</t>
+          <t>PTC India</t>
         </is>
       </c>
       <c r="B217" s="7" t="inlineStr">
         <is>
-          <t>https://jobs.paloaltonetworks.com/</t>
+          <t>https://www.ptc.com/en/careers</t>
         </is>
       </c>
       <c r="C217" s="6" t="inlineStr">
@@ -8038,31 +8908,35 @@
       </c>
       <c r="D217" s="6" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Design SW</t>
         </is>
       </c>
       <c r="E217" s="6" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="F217" s="6" t="inlineStr"/>
+          <t>Pune</t>
+        </is>
+      </c>
+      <c r="F217" s="6" t="n">
+        <v/>
+      </c>
       <c r="G217" s="6" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H217" s="6" t="inlineStr"/>
+      <c r="H217" s="6" t="n">
+        <v/>
+      </c>
     </row>
     <row r="218">
       <c r="A218" s="6" t="inlineStr">
         <is>
-          <t>PayPal India</t>
+          <t>Palo Alto Networks India</t>
         </is>
       </c>
       <c r="B218" s="7" t="inlineStr">
         <is>
-          <t>https://careers.pypl.com/</t>
+          <t>https://jobs.recruitee.com</t>
         </is>
       </c>
       <c r="C218" s="6" t="inlineStr">
@@ -8072,35 +8946,37 @@
       </c>
       <c r="D218" s="6" t="inlineStr">
         <is>
-          <t>Fintech</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="E218" s="6" t="inlineStr">
         <is>
-          <t>Chennai</t>
-        </is>
-      </c>
-      <c r="F218" s="6" t="inlineStr"/>
-      <c r="G218" s="8" t="inlineStr">
-        <is>
-          <t>Inactive</t>
-        </is>
-      </c>
-      <c r="H218" s="6" t="inlineStr">
-        <is>
-          <t>Workday/Taleo portal - not supported by scraper, enable only if audit verifies</t>
-        </is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
+      <c r="F218" s="6" t="inlineStr">
+        <is>
+          <t>recruitee</t>
+        </is>
+      </c>
+      <c r="G218" s="6" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="H218" s="6" t="n">
+        <v/>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="6" t="inlineStr">
         <is>
-          <t>Philips India</t>
+          <t>PayPal India</t>
         </is>
       </c>
       <c r="B219" s="7" t="inlineStr">
         <is>
-          <t>https://www.careers.philips.com/</t>
+          <t>https://careers.pypl.com/</t>
         </is>
       </c>
       <c r="C219" s="6" t="inlineStr">
@@ -8110,15 +8986,17 @@
       </c>
       <c r="D219" s="6" t="inlineStr">
         <is>
-          <t>HealthTech</t>
+          <t>Fintech</t>
         </is>
       </c>
       <c r="E219" s="6" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="F219" s="6" t="inlineStr"/>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="F219" s="6" t="n">
+        <v/>
+      </c>
       <c r="G219" s="8" t="inlineStr">
         <is>
           <t>Inactive</t>
@@ -8133,12 +9011,12 @@
     <row r="220">
       <c r="A220" s="6" t="inlineStr">
         <is>
-          <t>PTC India</t>
+          <t>Philips India</t>
         </is>
       </c>
       <c r="B220" s="7" t="inlineStr">
         <is>
-          <t>https://www.ptc.com/en/careers</t>
+          <t>https://www.careers.philips.com/</t>
         </is>
       </c>
       <c r="C220" s="6" t="inlineStr">
@@ -8148,21 +9026,27 @@
       </c>
       <c r="D220" s="6" t="inlineStr">
         <is>
-          <t>Design SW</t>
+          <t>HealthTech</t>
         </is>
       </c>
       <c r="E220" s="6" t="inlineStr">
         <is>
-          <t>Pune</t>
-        </is>
-      </c>
-      <c r="F220" s="6" t="inlineStr"/>
-      <c r="G220" s="6" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="H220" s="6" t="inlineStr"/>
+          <t>Bengaluru</t>
+        </is>
+      </c>
+      <c r="F220" s="6" t="n">
+        <v/>
+      </c>
+      <c r="G220" s="8" t="inlineStr">
+        <is>
+          <t>Inactive</t>
+        </is>
+      </c>
+      <c r="H220" s="6" t="inlineStr">
+        <is>
+          <t>Workday/Taleo portal - not supported by scraper, enable only if audit verifies</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" s="6" t="inlineStr">
@@ -8190,7 +9074,9 @@
           <t>Hyderabad</t>
         </is>
       </c>
-      <c r="F221" s="6" t="inlineStr"/>
+      <c r="F221" s="6" t="n">
+        <v/>
+      </c>
       <c r="G221" s="8" t="inlineStr">
         <is>
           <t>Inactive</t>
@@ -8228,7 +9114,9 @@
           <t>Pune</t>
         </is>
       </c>
-      <c r="F222" s="6" t="inlineStr"/>
+      <c r="F222" s="6" t="n">
+        <v/>
+      </c>
       <c r="G222" s="8" t="inlineStr">
         <is>
           <t>Inactive</t>
@@ -8248,7 +9136,7 @@
       </c>
       <c r="B223" s="7" t="inlineStr">
         <is>
-          <t>https://www.rubrik.com/company/careers</t>
+          <t>https://boards.greenhouse.io/rubrik</t>
         </is>
       </c>
       <c r="C223" s="6" t="inlineStr">
@@ -8266,23 +9154,29 @@
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="F223" s="6" t="inlineStr"/>
+      <c r="F223" s="6" t="inlineStr">
+        <is>
+          <t>greenhouse</t>
+        </is>
+      </c>
       <c r="G223" s="6" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H223" s="6" t="inlineStr"/>
+      <c r="H223" s="6" t="n">
+        <v/>
+      </c>
     </row>
     <row r="224">
       <c r="A224" s="6" t="inlineStr">
         <is>
-          <t>Salesforce India</t>
+          <t>SAP Labs India</t>
         </is>
       </c>
       <c r="B224" s="7" t="inlineStr">
         <is>
-          <t>https://careers.salesforce.com/en/jobs/</t>
+          <t>https://jobs.sap.com/</t>
         </is>
       </c>
       <c r="C224" s="6" t="inlineStr">
@@ -8292,31 +9186,37 @@
       </c>
       <c r="D224" s="6" t="inlineStr">
         <is>
-          <t>SaaS</t>
+          <t>Enterprise</t>
         </is>
       </c>
       <c r="E224" s="6" t="inlineStr">
         <is>
-          <t>Hyderabad</t>
-        </is>
-      </c>
-      <c r="F224" s="6" t="inlineStr"/>
-      <c r="G224" s="6" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="H224" s="6" t="inlineStr"/>
+          <t>Bengaluru</t>
+        </is>
+      </c>
+      <c r="F224" s="6" t="n">
+        <v/>
+      </c>
+      <c r="G224" s="8" t="inlineStr">
+        <is>
+          <t>Inactive</t>
+        </is>
+      </c>
+      <c r="H224" s="6" t="inlineStr">
+        <is>
+          <t>Workday/Taleo portal - not supported by scraper, enable only if audit verifies</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" s="6" t="inlineStr">
         <is>
-          <t>Samsung R&amp;D India</t>
+          <t>Salesforce India</t>
         </is>
       </c>
       <c r="B225" s="7" t="inlineStr">
         <is>
-          <t>https://www.samsung.com/in/about-us/careers/</t>
+          <t>https://careers.salesforce.com/en/jobs/</t>
         </is>
       </c>
       <c r="C225" s="6" t="inlineStr">
@@ -8326,31 +9226,35 @@
       </c>
       <c r="D225" s="6" t="inlineStr">
         <is>
-          <t>Electronics</t>
+          <t>SaaS</t>
         </is>
       </c>
       <c r="E225" s="6" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="F225" s="6" t="inlineStr"/>
+          <t>Hyderabad</t>
+        </is>
+      </c>
+      <c r="F225" s="6" t="n">
+        <v/>
+      </c>
       <c r="G225" s="6" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H225" s="6" t="inlineStr"/>
+      <c r="H225" s="6" t="n">
+        <v/>
+      </c>
     </row>
     <row r="226">
       <c r="A226" s="6" t="inlineStr">
         <is>
-          <t>SAP Labs India</t>
+          <t>Samsung R&amp;D India</t>
         </is>
       </c>
       <c r="B226" s="7" t="inlineStr">
         <is>
-          <t>https://jobs.sap.com/</t>
+          <t>https://samsung.recruitee.com</t>
         </is>
       </c>
       <c r="C226" s="6" t="inlineStr">
@@ -8360,7 +9264,7 @@
       </c>
       <c r="D226" s="6" t="inlineStr">
         <is>
-          <t>Enterprise</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="E226" s="6" t="inlineStr">
@@ -8368,16 +9272,18 @@
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="F226" s="6" t="inlineStr"/>
-      <c r="G226" s="8" t="inlineStr">
-        <is>
-          <t>Inactive</t>
-        </is>
-      </c>
-      <c r="H226" s="6" t="inlineStr">
-        <is>
-          <t>Workday/Taleo portal - not supported by scraper, enable only if audit verifies</t>
-        </is>
+      <c r="F226" s="6" t="inlineStr">
+        <is>
+          <t>recruitee</t>
+        </is>
+      </c>
+      <c r="G226" s="6" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="H226" s="6" t="n">
+        <v/>
       </c>
     </row>
     <row r="227">
@@ -8406,7 +9312,9 @@
           <t>Hyderabad</t>
         </is>
       </c>
-      <c r="F227" s="6" t="inlineStr"/>
+      <c r="F227" s="6" t="n">
+        <v/>
+      </c>
       <c r="G227" s="8" t="inlineStr">
         <is>
           <t>Inactive</t>
@@ -8444,7 +9352,9 @@
           <t>Pune</t>
         </is>
       </c>
-      <c r="F228" s="6" t="inlineStr"/>
+      <c r="F228" s="6" t="n">
+        <v/>
+      </c>
       <c r="G228" s="8" t="inlineStr">
         <is>
           <t>Inactive</t>
@@ -8464,7 +9374,7 @@
       </c>
       <c r="B229" s="7" t="inlineStr">
         <is>
-          <t>https://careers.snowflake.com/us/en/search-results</t>
+          <t>https://jobs.ashbyhq.com/snowflake</t>
         </is>
       </c>
       <c r="C229" s="6" t="inlineStr">
@@ -8482,13 +9392,19 @@
           <t>Pune</t>
         </is>
       </c>
-      <c r="F229" s="6" t="inlineStr"/>
+      <c r="F229" s="6" t="inlineStr">
+        <is>
+          <t>ashby</t>
+        </is>
+      </c>
       <c r="G229" s="6" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H229" s="6" t="inlineStr"/>
+      <c r="H229" s="6" t="n">
+        <v/>
+      </c>
     </row>
     <row r="230">
       <c r="A230" s="6" t="inlineStr">
@@ -8516,13 +9432,17 @@
           <t>Gurugram</t>
         </is>
       </c>
-      <c r="F230" s="6" t="inlineStr"/>
+      <c r="F230" s="6" t="n">
+        <v/>
+      </c>
       <c r="G230" s="6" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H230" s="6" t="inlineStr"/>
+      <c r="H230" s="6" t="n">
+        <v/>
+      </c>
     </row>
     <row r="231">
       <c r="A231" s="6" t="inlineStr">
@@ -8550,7 +9470,9 @@
           <t>Chennai</t>
         </is>
       </c>
-      <c r="F231" s="6" t="inlineStr"/>
+      <c r="F231" s="6" t="n">
+        <v/>
+      </c>
       <c r="G231" s="8" t="inlineStr">
         <is>
           <t>Inactive</t>
@@ -8570,7 +9492,7 @@
       </c>
       <c r="B232" s="7" t="inlineStr">
         <is>
-          <t>https://stripe.com/jobs/search</t>
+          <t>https://boards.greenhouse.io/stripe</t>
         </is>
       </c>
       <c r="C232" s="6" t="inlineStr">
@@ -8588,13 +9510,19 @@
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="F232" s="6" t="inlineStr"/>
+      <c r="F232" s="6" t="inlineStr">
+        <is>
+          <t>greenhouse</t>
+        </is>
+      </c>
       <c r="G232" s="6" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H232" s="6" t="inlineStr"/>
+      <c r="H232" s="6" t="n">
+        <v/>
+      </c>
     </row>
     <row r="233">
       <c r="A233" s="6" t="inlineStr">
@@ -8622,7 +9550,9 @@
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="F233" s="6" t="inlineStr"/>
+      <c r="F233" s="6" t="n">
+        <v/>
+      </c>
       <c r="G233" s="8" t="inlineStr">
         <is>
           <t>Inactive</t>
@@ -8660,7 +9590,9 @@
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="F234" s="6" t="inlineStr"/>
+      <c r="F234" s="6" t="n">
+        <v/>
+      </c>
       <c r="G234" s="8" t="inlineStr">
         <is>
           <t>Inactive</t>
@@ -8698,7 +9630,9 @@
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="F235" s="6" t="inlineStr"/>
+      <c r="F235" s="6" t="n">
+        <v/>
+      </c>
       <c r="G235" s="8" t="inlineStr">
         <is>
           <t>Inactive</t>
@@ -8736,7 +9670,9 @@
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="F236" s="6" t="inlineStr"/>
+      <c r="F236" s="6" t="n">
+        <v/>
+      </c>
       <c r="G236" s="8" t="inlineStr">
         <is>
           <t>Inactive</t>
@@ -8756,7 +9692,7 @@
       </c>
       <c r="B237" s="7" t="inlineStr">
         <is>
-          <t>https://www.twilio.com/en-us/company/jobs</t>
+          <t>https://boards.greenhouse.io/twilio</t>
         </is>
       </c>
       <c r="C237" s="6" t="inlineStr">
@@ -8774,23 +9710,29 @@
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="F237" s="6" t="inlineStr"/>
+      <c r="F237" s="6" t="inlineStr">
+        <is>
+          <t>greenhouse</t>
+        </is>
+      </c>
       <c r="G237" s="6" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H237" s="6" t="inlineStr"/>
+      <c r="H237" s="6" t="n">
+        <v/>
+      </c>
     </row>
     <row r="238">
       <c r="A238" s="6" t="inlineStr">
         <is>
-          <t>Uber India</t>
+          <t>UBS India</t>
         </is>
       </c>
       <c r="B238" s="7" t="inlineStr">
         <is>
-          <t>https://www.uber.com/us/en/careers/list/</t>
+          <t>https://www.ubs.com/global/en/careers.html</t>
         </is>
       </c>
       <c r="C238" s="6" t="inlineStr">
@@ -8800,31 +9742,37 @@
       </c>
       <c r="D238" s="6" t="inlineStr">
         <is>
-          <t>Mobility</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="E238" s="6" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="F238" s="6" t="inlineStr"/>
-      <c r="G238" s="6" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="H238" s="6" t="inlineStr"/>
+          <t>Pune</t>
+        </is>
+      </c>
+      <c r="F238" s="6" t="n">
+        <v/>
+      </c>
+      <c r="G238" s="8" t="inlineStr">
+        <is>
+          <t>Inactive</t>
+        </is>
+      </c>
+      <c r="H238" s="6" t="inlineStr">
+        <is>
+          <t>Workday/Taleo portal - not supported by scraper, enable only if audit verifies</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" s="6" t="inlineStr">
         <is>
-          <t>UBS India</t>
+          <t>Uber India</t>
         </is>
       </c>
       <c r="B239" s="7" t="inlineStr">
         <is>
-          <t>https://www.ubs.com/global/en/careers.html</t>
+          <t>https://careers.smartrecruiters.com/uber</t>
         </is>
       </c>
       <c r="C239" s="6" t="inlineStr">
@@ -8834,24 +9782,26 @@
       </c>
       <c r="D239" s="6" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Mobility</t>
         </is>
       </c>
       <c r="E239" s="6" t="inlineStr">
         <is>
-          <t>Pune</t>
-        </is>
-      </c>
-      <c r="F239" s="6" t="inlineStr"/>
-      <c r="G239" s="8" t="inlineStr">
-        <is>
-          <t>Inactive</t>
-        </is>
-      </c>
-      <c r="H239" s="6" t="inlineStr">
-        <is>
-          <t>Workday/Taleo portal - not supported by scraper, enable only if audit verifies</t>
-        </is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
+      <c r="F239" s="6" t="inlineStr">
+        <is>
+          <t>smartrecruiters</t>
+        </is>
+      </c>
+      <c r="G239" s="6" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="H239" s="6" t="n">
+        <v/>
       </c>
     </row>
     <row r="240">
@@ -8880,7 +9830,9 @@
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="F240" s="6" t="inlineStr"/>
+      <c r="F240" s="6" t="n">
+        <v/>
+      </c>
       <c r="G240" s="8" t="inlineStr">
         <is>
           <t>Inactive</t>
@@ -8918,7 +9870,9 @@
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="F241" s="6" t="inlineStr"/>
+      <c r="F241" s="6" t="n">
+        <v/>
+      </c>
       <c r="G241" s="8" t="inlineStr">
         <is>
           <t>Inactive</t>
@@ -8956,7 +9910,9 @@
           <t>Hyderabad</t>
         </is>
       </c>
-      <c r="F242" s="6" t="inlineStr"/>
+      <c r="F242" s="6" t="n">
+        <v/>
+      </c>
       <c r="G242" s="8" t="inlineStr">
         <is>
           <t>Inactive</t>
@@ -8969,14 +9925,14 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="6" t="inlineStr">
+      <c r="A243" s="9" t="inlineStr">
         <is>
           <t>Western Digital India</t>
         </is>
       </c>
       <c r="B243" s="7" t="inlineStr">
         <is>
-          <t>https://jobs.westerndigital.com/</t>
+          <t>https://careers.smartrecruiters.com/WesternDigital</t>
         </is>
       </c>
       <c r="C243" s="6" t="inlineStr">
@@ -8994,15 +9950,19 @@
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="F243" s="6" t="inlineStr"/>
-      <c r="G243" s="8" t="inlineStr">
-        <is>
-          <t>Inactive</t>
+      <c r="F243" s="6" t="inlineStr">
+        <is>
+          <t>smartrecruiters</t>
+        </is>
+      </c>
+      <c r="G243" s="6" t="inlineStr">
+        <is>
+          <t>Active</t>
         </is>
       </c>
       <c r="H243" s="6" t="inlineStr">
         <is>
-          <t>Workday/Taleo portal - not supported by scraper, enable only if audit verifies</t>
+          <t>Workday/Taleo portal - not supported by scraper, enable only if audit verifies | Auto-verified token, worth a quick manual sanity check.</t>
         </is>
       </c>
     </row>
@@ -9032,7 +9992,9 @@
           <t>Pune</t>
         </is>
       </c>
-      <c r="F244" s="6" t="inlineStr"/>
+      <c r="F244" s="6" t="n">
+        <v/>
+      </c>
       <c r="G244" s="8" t="inlineStr">
         <is>
           <t>Inactive</t>
@@ -9070,13 +10032,17 @@
           <t>Chennai</t>
         </is>
       </c>
-      <c r="F245" s="6" t="inlineStr"/>
+      <c r="F245" s="6" t="n">
+        <v/>
+      </c>
       <c r="G245" s="6" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H245" s="6" t="inlineStr"/>
+      <c r="H245" s="6" t="n">
+        <v/>
+      </c>
     </row>
     <row r="246">
       <c r="A246" s="6" t="inlineStr">
@@ -9104,13 +10070,17 @@
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="F246" s="6" t="inlineStr"/>
+      <c r="F246" s="6" t="n">
+        <v/>
+      </c>
       <c r="G246" s="6" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H246" s="6" t="inlineStr"/>
+      <c r="H246" s="6" t="n">
+        <v/>
+      </c>
     </row>
     <row r="247">
       <c r="A247" s="6" t="inlineStr">
@@ -9120,7 +10090,7 @@
       </c>
       <c r="B247" s="7" t="inlineStr">
         <is>
-          <t>https://www.zscaler.com/careers</t>
+          <t>https://boards.greenhouse.io/zscaler</t>
         </is>
       </c>
       <c r="C247" s="6" t="inlineStr">
@@ -9138,1327 +10108,1465 @@
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="F247" s="6" t="inlineStr"/>
+      <c r="F247" s="6" t="inlineStr">
+        <is>
+          <t>greenhouse</t>
+        </is>
+      </c>
       <c r="G247" s="6" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="H247" s="6" t="inlineStr"/>
+      <c r="H247" s="6" t="n">
+        <v/>
+      </c>
     </row>
     <row r="248">
-      <c r="A248" s="9" t="inlineStr">
+      <c r="A248" s="10" t="inlineStr">
         <is>
           <t>Accenture India</t>
         </is>
       </c>
-      <c r="B248" s="10" t="inlineStr">
-        <is>
-          <t>https://www.accenture.com/in-en/careers</t>
-        </is>
-      </c>
-      <c r="C248" s="9" t="inlineStr">
+      <c r="B248" s="11" t="inlineStr">
+        <is>
+          <t>https://accenture.recruitee.com</t>
+        </is>
+      </c>
+      <c r="C248" s="10" t="inlineStr">
         <is>
           <t>Indian IT Services</t>
         </is>
       </c>
-      <c r="D248" s="9" t="inlineStr">
+      <c r="D248" s="10" t="inlineStr">
         <is>
           <t>Consulting</t>
         </is>
       </c>
-      <c r="E248" s="9" t="inlineStr">
-        <is>
-          <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="F248" s="9" t="inlineStr"/>
-      <c r="G248" s="11" t="inlineStr">
+      <c r="E248" s="10" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
+      <c r="F248" s="10" t="inlineStr">
+        <is>
+          <t>recruitee</t>
+        </is>
+      </c>
+      <c r="G248" s="10" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="H248" s="10" t="inlineStr">
+        <is>
+          <t>Freshers hired via mass drives (NQT/HackWithInfy etc), not this board</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="10" t="inlineStr">
+        <is>
+          <t>Birlasoft</t>
+        </is>
+      </c>
+      <c r="B249" s="11" t="inlineStr">
+        <is>
+          <t>https://www.birlasoft.com/careers</t>
+        </is>
+      </c>
+      <c r="C249" s="10" t="inlineStr">
+        <is>
+          <t>Indian IT Services</t>
+        </is>
+      </c>
+      <c r="D249" s="10" t="inlineStr">
+        <is>
+          <t>IT Services</t>
+        </is>
+      </c>
+      <c r="E249" s="10" t="inlineStr">
+        <is>
+          <t>Noida</t>
+        </is>
+      </c>
+      <c r="F249" s="10" t="n">
+        <v/>
+      </c>
+      <c r="G249" s="10" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="H249" s="10" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="10" t="inlineStr">
+        <is>
+          <t>Capgemini India</t>
+        </is>
+      </c>
+      <c r="B250" s="11" t="inlineStr">
+        <is>
+          <t>https://www.capgemini.com/careers/</t>
+        </is>
+      </c>
+      <c r="C250" s="10" t="inlineStr">
+        <is>
+          <t>Indian IT Services</t>
+        </is>
+      </c>
+      <c r="D250" s="10" t="inlineStr">
+        <is>
+          <t>IT Services</t>
+        </is>
+      </c>
+      <c r="E250" s="10" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="F250" s="10" t="n">
+        <v/>
+      </c>
+      <c r="G250" s="12" t="inlineStr">
         <is>
           <t>Inactive</t>
         </is>
       </c>
-      <c r="H248" s="9" t="inlineStr">
+      <c r="H250" s="10" t="inlineStr">
         <is>
           <t>Freshers hired via mass drives (NQT/HackWithInfy etc), not this board</t>
         </is>
       </c>
     </row>
-    <row r="249">
-      <c r="A249" s="9" t="inlineStr">
-        <is>
-          <t>Birlasoft</t>
-        </is>
-      </c>
-      <c r="B249" s="10" t="inlineStr">
-        <is>
-          <t>https://www.birlasoft.com/careers</t>
-        </is>
-      </c>
-      <c r="C249" s="9" t="inlineStr">
+    <row r="251">
+      <c r="A251" s="10" t="inlineStr">
+        <is>
+          <t>Cigniti Technologies</t>
+        </is>
+      </c>
+      <c r="B251" s="11" t="inlineStr">
+        <is>
+          <t>https://www.cigniti.com/careers/</t>
+        </is>
+      </c>
+      <c r="C251" s="10" t="inlineStr">
         <is>
           <t>Indian IT Services</t>
         </is>
       </c>
-      <c r="D249" s="9" t="inlineStr">
+      <c r="D251" s="10" t="inlineStr">
+        <is>
+          <t>QA / Testing</t>
+        </is>
+      </c>
+      <c r="E251" s="10" t="inlineStr">
+        <is>
+          <t>Hyderabad</t>
+        </is>
+      </c>
+      <c r="F251" s="10" t="n">
+        <v/>
+      </c>
+      <c r="G251" s="10" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="H251" s="10" t="inlineStr">
+        <is>
+          <t>Testing-focused - good for QA freshers</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="10" t="inlineStr">
+        <is>
+          <t>Coforge</t>
+        </is>
+      </c>
+      <c r="B252" s="11" t="inlineStr">
+        <is>
+          <t>https://www.coforge.com/careers</t>
+        </is>
+      </c>
+      <c r="C252" s="10" t="inlineStr">
+        <is>
+          <t>Indian IT Services</t>
+        </is>
+      </c>
+      <c r="D252" s="10" t="inlineStr">
         <is>
           <t>IT Services</t>
         </is>
       </c>
-      <c r="E249" s="9" t="inlineStr">
+      <c r="E252" s="10" t="inlineStr">
         <is>
           <t>Noida</t>
         </is>
       </c>
-      <c r="F249" s="9" t="inlineStr"/>
-      <c r="G249" s="9" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="H249" s="9" t="inlineStr"/>
-    </row>
-    <row r="250">
-      <c r="A250" s="9" t="inlineStr">
-        <is>
-          <t>Capgemini India</t>
-        </is>
-      </c>
-      <c r="B250" s="10" t="inlineStr">
-        <is>
-          <t>https://www.capgemini.com/careers/</t>
-        </is>
-      </c>
-      <c r="C250" s="9" t="inlineStr">
+      <c r="F252" s="10" t="n">
+        <v/>
+      </c>
+      <c r="G252" s="10" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="H252" s="10" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="10" t="inlineStr">
+        <is>
+          <t>Cognizant</t>
+        </is>
+      </c>
+      <c r="B253" s="11" t="inlineStr">
+        <is>
+          <t>https://careers.cognizant.com/global/en</t>
+        </is>
+      </c>
+      <c r="C253" s="10" t="inlineStr">
         <is>
           <t>Indian IT Services</t>
         </is>
       </c>
-      <c r="D250" s="9" t="inlineStr">
+      <c r="D253" s="10" t="inlineStr">
         <is>
           <t>IT Services</t>
         </is>
       </c>
-      <c r="E250" s="9" t="inlineStr">
+      <c r="E253" s="10" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="F253" s="10" t="n">
+        <v/>
+      </c>
+      <c r="G253" s="12" t="inlineStr">
+        <is>
+          <t>Inactive</t>
+        </is>
+      </c>
+      <c r="H253" s="10" t="inlineStr">
+        <is>
+          <t>Freshers hired via mass drives (NQT/HackWithInfy etc), not this board</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="10" t="inlineStr">
+        <is>
+          <t>Cyient</t>
+        </is>
+      </c>
+      <c r="B254" s="11" t="inlineStr">
+        <is>
+          <t>https://www.cyient.com/careers</t>
+        </is>
+      </c>
+      <c r="C254" s="10" t="inlineStr">
+        <is>
+          <t>Indian IT Services</t>
+        </is>
+      </c>
+      <c r="D254" s="10" t="inlineStr">
+        <is>
+          <t>Engineering Services</t>
+        </is>
+      </c>
+      <c r="E254" s="10" t="inlineStr">
+        <is>
+          <t>Hyderabad</t>
+        </is>
+      </c>
+      <c r="F254" s="10" t="n">
+        <v/>
+      </c>
+      <c r="G254" s="10" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="H254" s="10" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="13" t="inlineStr">
+        <is>
+          <t>Genpact</t>
+        </is>
+      </c>
+      <c r="B255" s="11" t="inlineStr">
+        <is>
+          <t>https://careers.smartrecruiters.com/genpactindia</t>
+        </is>
+      </c>
+      <c r="C255" s="10" t="inlineStr">
+        <is>
+          <t>Indian IT Services</t>
+        </is>
+      </c>
+      <c r="D255" s="10" t="inlineStr">
+        <is>
+          <t>BPM/Tech</t>
+        </is>
+      </c>
+      <c r="E255" s="10" t="inlineStr">
+        <is>
+          <t>Gurugram</t>
+        </is>
+      </c>
+      <c r="F255" s="10" t="inlineStr">
+        <is>
+          <t>smartrecruiters</t>
+        </is>
+      </c>
+      <c r="G255" s="10" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="H255" s="10" t="inlineStr">
+        <is>
+          <t>Freshers hired via mass drives (NQT/HackWithInfy etc), not this board | Auto-verified token, worth a quick manual sanity check.</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="10" t="inlineStr">
+        <is>
+          <t>HCLTech</t>
+        </is>
+      </c>
+      <c r="B256" s="11" t="inlineStr">
+        <is>
+          <t>https://www.hcltech.com/careers</t>
+        </is>
+      </c>
+      <c r="C256" s="10" t="inlineStr">
+        <is>
+          <t>Indian IT Services</t>
+        </is>
+      </c>
+      <c r="D256" s="10" t="inlineStr">
+        <is>
+          <t>IT Services</t>
+        </is>
+      </c>
+      <c r="E256" s="10" t="inlineStr">
+        <is>
+          <t>Noida</t>
+        </is>
+      </c>
+      <c r="F256" s="10" t="n">
+        <v/>
+      </c>
+      <c r="G256" s="12" t="inlineStr">
+        <is>
+          <t>Inactive</t>
+        </is>
+      </c>
+      <c r="H256" s="10" t="inlineStr">
+        <is>
+          <t>Freshers hired via mass drives (NQT/HackWithInfy etc), not this board</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="10" t="inlineStr">
+        <is>
+          <t>Happiest Minds</t>
+        </is>
+      </c>
+      <c r="B257" s="11" t="inlineStr">
+        <is>
+          <t>https://www.happiestminds.com/careers/</t>
+        </is>
+      </c>
+      <c r="C257" s="10" t="inlineStr">
+        <is>
+          <t>Indian IT Services</t>
+        </is>
+      </c>
+      <c r="D257" s="10" t="inlineStr">
+        <is>
+          <t>IT Services</t>
+        </is>
+      </c>
+      <c r="E257" s="10" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
+      <c r="F257" s="10" t="n">
+        <v/>
+      </c>
+      <c r="G257" s="10" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="H257" s="10" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="10" t="inlineStr">
+        <is>
+          <t>Hexaware</t>
+        </is>
+      </c>
+      <c r="B258" s="11" t="inlineStr">
+        <is>
+          <t>https://hexaware.com/careers/</t>
+        </is>
+      </c>
+      <c r="C258" s="10" t="inlineStr">
+        <is>
+          <t>Indian IT Services</t>
+        </is>
+      </c>
+      <c r="D258" s="10" t="inlineStr">
+        <is>
+          <t>IT Services</t>
+        </is>
+      </c>
+      <c r="E258" s="10" t="inlineStr">
         <is>
           <t>Mumbai</t>
         </is>
       </c>
-      <c r="F250" s="9" t="inlineStr"/>
-      <c r="G250" s="11" t="inlineStr">
+      <c r="F258" s="10" t="n">
+        <v/>
+      </c>
+      <c r="G258" s="10" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="H258" s="10" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="10" t="inlineStr">
+        <is>
+          <t>Infosys</t>
+        </is>
+      </c>
+      <c r="B259" s="11" t="inlineStr">
+        <is>
+          <t>https://www.infosys.com/careers/</t>
+        </is>
+      </c>
+      <c r="C259" s="10" t="inlineStr">
+        <is>
+          <t>Indian IT Services</t>
+        </is>
+      </c>
+      <c r="D259" s="10" t="inlineStr">
+        <is>
+          <t>IT Services</t>
+        </is>
+      </c>
+      <c r="E259" s="10" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
+      <c r="F259" s="10" t="n">
+        <v/>
+      </c>
+      <c r="G259" s="12" t="inlineStr">
         <is>
           <t>Inactive</t>
         </is>
       </c>
-      <c r="H250" s="9" t="inlineStr">
+      <c r="H259" s="10" t="inlineStr">
         <is>
           <t>Freshers hired via mass drives (NQT/HackWithInfy etc), not this board</t>
         </is>
       </c>
     </row>
-    <row r="251">
-      <c r="A251" s="9" t="inlineStr">
-        <is>
-          <t>Cigniti Technologies</t>
-        </is>
-      </c>
-      <c r="B251" s="10" t="inlineStr">
-        <is>
-          <t>https://www.cigniti.com/careers/</t>
-        </is>
-      </c>
-      <c r="C251" s="9" t="inlineStr">
+    <row r="260">
+      <c r="A260" s="10" t="inlineStr">
+        <is>
+          <t>Infosys BPM</t>
+        </is>
+      </c>
+      <c r="B260" s="11" t="inlineStr">
+        <is>
+          <t>https://www.infosysbpm.com/careers.html</t>
+        </is>
+      </c>
+      <c r="C260" s="10" t="inlineStr">
         <is>
           <t>Indian IT Services</t>
         </is>
       </c>
-      <c r="D251" s="9" t="inlineStr">
+      <c r="D260" s="10" t="inlineStr">
+        <is>
+          <t>BPM/Tech</t>
+        </is>
+      </c>
+      <c r="E260" s="10" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
+      <c r="F260" s="10" t="n">
+        <v/>
+      </c>
+      <c r="G260" s="12" t="inlineStr">
+        <is>
+          <t>Inactive</t>
+        </is>
+      </c>
+      <c r="H260" s="10" t="inlineStr">
+        <is>
+          <t>Freshers hired via mass drives (NQT/HackWithInfy etc), not this board</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="10" t="inlineStr">
+        <is>
+          <t>Intellect Design Arena</t>
+        </is>
+      </c>
+      <c r="B261" s="11" t="inlineStr">
+        <is>
+          <t>https://www.intellectdesign.com/careers/</t>
+        </is>
+      </c>
+      <c r="C261" s="10" t="inlineStr">
+        <is>
+          <t>Indian IT Services</t>
+        </is>
+      </c>
+      <c r="D261" s="10" t="inlineStr">
+        <is>
+          <t>FinTech Product</t>
+        </is>
+      </c>
+      <c r="E261" s="10" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="F261" s="10" t="n">
+        <v/>
+      </c>
+      <c r="G261" s="10" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="H261" s="10" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="10" t="inlineStr">
+        <is>
+          <t>KPIT Technologies</t>
+        </is>
+      </c>
+      <c r="B262" s="11" t="inlineStr">
+        <is>
+          <t>https://www.kpit.com/careers/</t>
+        </is>
+      </c>
+      <c r="C262" s="10" t="inlineStr">
+        <is>
+          <t>Indian IT Services</t>
+        </is>
+      </c>
+      <c r="D262" s="10" t="inlineStr">
+        <is>
+          <t>Automotive SW</t>
+        </is>
+      </c>
+      <c r="E262" s="10" t="inlineStr">
+        <is>
+          <t>Pune</t>
+        </is>
+      </c>
+      <c r="F262" s="10" t="n">
+        <v/>
+      </c>
+      <c r="G262" s="10" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="H262" s="10" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="10" t="inlineStr">
+        <is>
+          <t>L&amp;T Technology Services</t>
+        </is>
+      </c>
+      <c r="B263" s="11" t="inlineStr">
+        <is>
+          <t>https://www.ltts.com/careers</t>
+        </is>
+      </c>
+      <c r="C263" s="10" t="inlineStr">
+        <is>
+          <t>Indian IT Services</t>
+        </is>
+      </c>
+      <c r="D263" s="10" t="inlineStr">
+        <is>
+          <t>Engineering Services</t>
+        </is>
+      </c>
+      <c r="E263" s="10" t="inlineStr">
+        <is>
+          <t>Vadodara</t>
+        </is>
+      </c>
+      <c r="F263" s="10" t="n">
+        <v/>
+      </c>
+      <c r="G263" s="10" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="H263" s="10" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="10" t="inlineStr">
+        <is>
+          <t>LTIMindtree</t>
+        </is>
+      </c>
+      <c r="B264" s="11" t="inlineStr">
+        <is>
+          <t>https://www.ltimindtree.com/careers/</t>
+        </is>
+      </c>
+      <c r="C264" s="10" t="inlineStr">
+        <is>
+          <t>Indian IT Services</t>
+        </is>
+      </c>
+      <c r="D264" s="10" t="inlineStr">
+        <is>
+          <t>IT Services</t>
+        </is>
+      </c>
+      <c r="E264" s="10" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="F264" s="10" t="n">
+        <v/>
+      </c>
+      <c r="G264" s="12" t="inlineStr">
+        <is>
+          <t>Inactive</t>
+        </is>
+      </c>
+      <c r="H264" s="10" t="inlineStr">
+        <is>
+          <t>Freshers hired via mass drives (NQT/HackWithInfy etc), not this board</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="10" t="inlineStr">
+        <is>
+          <t>Mastek</t>
+        </is>
+      </c>
+      <c r="B265" s="11" t="inlineStr">
+        <is>
+          <t>https://www.mastek.com/careers</t>
+        </is>
+      </c>
+      <c r="C265" s="10" t="inlineStr">
+        <is>
+          <t>Indian IT Services</t>
+        </is>
+      </c>
+      <c r="D265" s="10" t="inlineStr">
+        <is>
+          <t>IT Services</t>
+        </is>
+      </c>
+      <c r="E265" s="10" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="F265" s="10" t="n">
+        <v/>
+      </c>
+      <c r="G265" s="10" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="H265" s="10" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="10" t="inlineStr">
+        <is>
+          <t>Mphasis</t>
+        </is>
+      </c>
+      <c r="B266" s="11" t="inlineStr">
+        <is>
+          <t>https://careers.mphasis.com/</t>
+        </is>
+      </c>
+      <c r="C266" s="10" t="inlineStr">
+        <is>
+          <t>Indian IT Services</t>
+        </is>
+      </c>
+      <c r="D266" s="10" t="inlineStr">
+        <is>
+          <t>IT Services</t>
+        </is>
+      </c>
+      <c r="E266" s="10" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
+      <c r="F266" s="10" t="n">
+        <v/>
+      </c>
+      <c r="G266" s="10" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="H266" s="10" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="10" t="inlineStr">
+        <is>
+          <t>Newgen Software</t>
+        </is>
+      </c>
+      <c r="B267" s="11" t="inlineStr">
+        <is>
+          <t>https://newgensoft.com/careers/</t>
+        </is>
+      </c>
+      <c r="C267" s="10" t="inlineStr">
+        <is>
+          <t>Indian IT Services</t>
+        </is>
+      </c>
+      <c r="D267" s="10" t="inlineStr">
+        <is>
+          <t>Product/Services</t>
+        </is>
+      </c>
+      <c r="E267" s="10" t="inlineStr">
+        <is>
+          <t>Noida</t>
+        </is>
+      </c>
+      <c r="F267" s="10" t="n">
+        <v/>
+      </c>
+      <c r="G267" s="10" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="H267" s="10" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="10" t="inlineStr">
+        <is>
+          <t>Nucleus Software</t>
+        </is>
+      </c>
+      <c r="B268" s="11" t="inlineStr">
+        <is>
+          <t>https://www.nucleussoftware.com/careers</t>
+        </is>
+      </c>
+      <c r="C268" s="10" t="inlineStr">
+        <is>
+          <t>Indian IT Services</t>
+        </is>
+      </c>
+      <c r="D268" s="10" t="inlineStr">
+        <is>
+          <t>FinTech Product</t>
+        </is>
+      </c>
+      <c r="E268" s="10" t="inlineStr">
+        <is>
+          <t>Noida</t>
+        </is>
+      </c>
+      <c r="F268" s="10" t="n">
+        <v/>
+      </c>
+      <c r="G268" s="10" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="H268" s="10" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="10" t="inlineStr">
+        <is>
+          <t>Persistent Systems</t>
+        </is>
+      </c>
+      <c r="B269" s="11" t="inlineStr">
+        <is>
+          <t>https://www.persistent.com/careers/</t>
+        </is>
+      </c>
+      <c r="C269" s="10" t="inlineStr">
+        <is>
+          <t>Indian IT Services</t>
+        </is>
+      </c>
+      <c r="D269" s="10" t="inlineStr">
+        <is>
+          <t>IT Services</t>
+        </is>
+      </c>
+      <c r="E269" s="10" t="inlineStr">
+        <is>
+          <t>Pune</t>
+        </is>
+      </c>
+      <c r="F269" s="10" t="n">
+        <v/>
+      </c>
+      <c r="G269" s="10" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="H269" s="10" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="10" t="inlineStr">
+        <is>
+          <t>Publicis Sapient India</t>
+        </is>
+      </c>
+      <c r="B270" s="11" t="inlineStr">
+        <is>
+          <t>https://careers.publicissapient.com/</t>
+        </is>
+      </c>
+      <c r="C270" s="10" t="inlineStr">
+        <is>
+          <t>Indian IT Services</t>
+        </is>
+      </c>
+      <c r="D270" s="10" t="inlineStr">
+        <is>
+          <t>Consulting</t>
+        </is>
+      </c>
+      <c r="E270" s="10" t="inlineStr">
+        <is>
+          <t>Gurugram</t>
+        </is>
+      </c>
+      <c r="F270" s="10" t="n">
+        <v/>
+      </c>
+      <c r="G270" s="10" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="H270" s="10" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="10" t="inlineStr">
+        <is>
+          <t>Qualitest India</t>
+        </is>
+      </c>
+      <c r="B271" s="11" t="inlineStr">
+        <is>
+          <t>https://careers.smartrecruiters.com/qualitestgroup</t>
+        </is>
+      </c>
+      <c r="C271" s="10" t="inlineStr">
+        <is>
+          <t>Indian IT Services</t>
+        </is>
+      </c>
+      <c r="D271" s="10" t="inlineStr">
         <is>
           <t>QA / Testing</t>
         </is>
       </c>
-      <c r="E251" s="9" t="inlineStr">
-        <is>
-          <t>Hyderabad</t>
-        </is>
-      </c>
-      <c r="F251" s="9" t="inlineStr"/>
-      <c r="G251" s="9" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="H251" s="9" t="inlineStr">
+      <c r="E271" s="10" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
+      <c r="F271" s="10" t="inlineStr">
+        <is>
+          <t>smartrecruiters</t>
+        </is>
+      </c>
+      <c r="G271" s="10" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="H271" s="10" t="inlineStr">
         <is>
           <t>Testing-focused - good for QA freshers</t>
         </is>
       </c>
     </row>
-    <row r="252">
-      <c r="A252" s="9" t="inlineStr">
-        <is>
-          <t>Coforge</t>
-        </is>
-      </c>
-      <c r="B252" s="10" t="inlineStr">
-        <is>
-          <t>https://www.coforge.com/careers</t>
-        </is>
-      </c>
-      <c r="C252" s="9" t="inlineStr">
+    <row r="272">
+      <c r="A272" s="10" t="inlineStr">
+        <is>
+          <t>Quest Global</t>
+        </is>
+      </c>
+      <c r="B272" s="11" t="inlineStr">
+        <is>
+          <t>https://careers.smartrecruiters.com/questglobaltechnologies</t>
+        </is>
+      </c>
+      <c r="C272" s="10" t="inlineStr">
         <is>
           <t>Indian IT Services</t>
         </is>
       </c>
-      <c r="D252" s="9" t="inlineStr">
+      <c r="D272" s="10" t="inlineStr">
+        <is>
+          <t>Engineering Services</t>
+        </is>
+      </c>
+      <c r="E272" s="10" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
+      <c r="F272" s="10" t="inlineStr">
+        <is>
+          <t>smartrecruiters</t>
+        </is>
+      </c>
+      <c r="G272" s="10" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="H272" s="10" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="10" t="inlineStr">
+        <is>
+          <t>Ramco Systems</t>
+        </is>
+      </c>
+      <c r="B273" s="11" t="inlineStr">
+        <is>
+          <t>https://www.ramco.com/careers/</t>
+        </is>
+      </c>
+      <c r="C273" s="10" t="inlineStr">
+        <is>
+          <t>Indian IT Services</t>
+        </is>
+      </c>
+      <c r="D273" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise SW</t>
+        </is>
+      </c>
+      <c r="E273" s="10" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="F273" s="10" t="n">
+        <v/>
+      </c>
+      <c r="G273" s="10" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="H273" s="10" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="10" t="inlineStr">
+        <is>
+          <t>Sasken Technologies</t>
+        </is>
+      </c>
+      <c r="B274" s="11" t="inlineStr">
+        <is>
+          <t>https://www.sasken.com/careers</t>
+        </is>
+      </c>
+      <c r="C274" s="10" t="inlineStr">
+        <is>
+          <t>Indian IT Services</t>
+        </is>
+      </c>
+      <c r="D274" s="10" t="inlineStr">
+        <is>
+          <t>Engineering Services</t>
+        </is>
+      </c>
+      <c r="E274" s="10" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
+      <c r="F274" s="10" t="n">
+        <v/>
+      </c>
+      <c r="G274" s="10" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="H274" s="10" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="10" t="inlineStr">
+        <is>
+          <t>Sonata Software</t>
+        </is>
+      </c>
+      <c r="B275" s="11" t="inlineStr">
+        <is>
+          <t>https://www.sonata-software.com/careers</t>
+        </is>
+      </c>
+      <c r="C275" s="10" t="inlineStr">
+        <is>
+          <t>Indian IT Services</t>
+        </is>
+      </c>
+      <c r="D275" s="10" t="inlineStr">
         <is>
           <t>IT Services</t>
         </is>
       </c>
-      <c r="E252" s="9" t="inlineStr">
-        <is>
-          <t>Noida</t>
-        </is>
-      </c>
-      <c r="F252" s="9" t="inlineStr"/>
-      <c r="G252" s="9" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="H252" s="9" t="inlineStr"/>
-    </row>
-    <row r="253">
-      <c r="A253" s="9" t="inlineStr">
-        <is>
-          <t>Cognizant</t>
-        </is>
-      </c>
-      <c r="B253" s="10" t="inlineStr">
-        <is>
-          <t>https://careers.cognizant.com/global/en</t>
-        </is>
-      </c>
-      <c r="C253" s="9" t="inlineStr">
+      <c r="E275" s="10" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
+      <c r="F275" s="10" t="n">
+        <v/>
+      </c>
+      <c r="G275" s="10" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="H275" s="10" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="10" t="inlineStr">
+        <is>
+          <t>Subex</t>
+        </is>
+      </c>
+      <c r="B276" s="11" t="inlineStr">
+        <is>
+          <t>https://www.subex.com/careers/</t>
+        </is>
+      </c>
+      <c r="C276" s="10" t="inlineStr">
         <is>
           <t>Indian IT Services</t>
         </is>
       </c>
-      <c r="D253" s="9" t="inlineStr">
+      <c r="D276" s="10" t="inlineStr">
+        <is>
+          <t>Telecom SW</t>
+        </is>
+      </c>
+      <c r="E276" s="10" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
+      <c r="F276" s="10" t="n">
+        <v/>
+      </c>
+      <c r="G276" s="10" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="H276" s="10" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="13" t="inlineStr">
+        <is>
+          <t>TCS</t>
+        </is>
+      </c>
+      <c r="B277" s="11" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/tcs</t>
+        </is>
+      </c>
+      <c r="C277" s="10" t="inlineStr">
+        <is>
+          <t>Indian IT Services</t>
+        </is>
+      </c>
+      <c r="D277" s="10" t="inlineStr">
         <is>
           <t>IT Services</t>
         </is>
       </c>
-      <c r="E253" s="9" t="inlineStr">
-        <is>
-          <t>Chennai</t>
-        </is>
-      </c>
-      <c r="F253" s="9" t="inlineStr"/>
-      <c r="G253" s="11" t="inlineStr">
+      <c r="E277" s="10" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="F277" s="10" t="inlineStr">
+        <is>
+          <t>greenhouse</t>
+        </is>
+      </c>
+      <c r="G277" s="10" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="H277" s="10" t="inlineStr">
+        <is>
+          <t>Freshers hired via mass drives (NQT/HackWithInfy etc), not this board | Auto-verified token, worth a quick manual sanity check.</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="10" t="inlineStr">
+        <is>
+          <t>Tata Elxsi</t>
+        </is>
+      </c>
+      <c r="B278" s="11" t="inlineStr">
+        <is>
+          <t>https://www.tataelxsi.com/careers</t>
+        </is>
+      </c>
+      <c r="C278" s="10" t="inlineStr">
+        <is>
+          <t>Indian IT Services</t>
+        </is>
+      </c>
+      <c r="D278" s="10" t="inlineStr">
+        <is>
+          <t>Engineering Services</t>
+        </is>
+      </c>
+      <c r="E278" s="10" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
+      <c r="F278" s="10" t="n">
+        <v/>
+      </c>
+      <c r="G278" s="10" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="H278" s="10" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="10" t="inlineStr">
+        <is>
+          <t>Tech Mahindra</t>
+        </is>
+      </c>
+      <c r="B279" s="11" t="inlineStr">
+        <is>
+          <t>https://careers.techmahindra.com/</t>
+        </is>
+      </c>
+      <c r="C279" s="10" t="inlineStr">
+        <is>
+          <t>Indian IT Services</t>
+        </is>
+      </c>
+      <c r="D279" s="10" t="inlineStr">
+        <is>
+          <t>IT Services</t>
+        </is>
+      </c>
+      <c r="E279" s="10" t="inlineStr">
+        <is>
+          <t>Pune</t>
+        </is>
+      </c>
+      <c r="F279" s="10" t="n">
+        <v/>
+      </c>
+      <c r="G279" s="12" t="inlineStr">
         <is>
           <t>Inactive</t>
         </is>
       </c>
-      <c r="H253" s="9" t="inlineStr">
+      <c r="H279" s="10" t="inlineStr">
         <is>
           <t>Freshers hired via mass drives (NQT/HackWithInfy etc), not this board</t>
         </is>
       </c>
     </row>
-    <row r="254">
-      <c r="A254" s="9" t="inlineStr">
-        <is>
-          <t>Cyient</t>
-        </is>
-      </c>
-      <c r="B254" s="10" t="inlineStr">
-        <is>
-          <t>https://www.cyient.com/careers</t>
-        </is>
-      </c>
-      <c r="C254" s="9" t="inlineStr">
+    <row r="280">
+      <c r="A280" s="10" t="inlineStr">
+        <is>
+          <t>Thoughtworks India</t>
+        </is>
+      </c>
+      <c r="B280" s="11" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/thoughtworks</t>
+        </is>
+      </c>
+      <c r="C280" s="10" t="inlineStr">
         <is>
           <t>Indian IT Services</t>
         </is>
       </c>
-      <c r="D254" s="9" t="inlineStr">
+      <c r="D280" s="10" t="inlineStr">
+        <is>
+          <t>Consulting</t>
+        </is>
+      </c>
+      <c r="E280" s="10" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
+      <c r="F280" s="10" t="inlineStr">
+        <is>
+          <t>greenhouse</t>
+        </is>
+      </c>
+      <c r="G280" s="10" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="H280" s="10" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="10" t="inlineStr">
+        <is>
+          <t>WNS Global</t>
+        </is>
+      </c>
+      <c r="B281" s="11" t="inlineStr">
+        <is>
+          <t>https://www.wns.com/careers</t>
+        </is>
+      </c>
+      <c r="C281" s="10" t="inlineStr">
+        <is>
+          <t>Indian IT Services</t>
+        </is>
+      </c>
+      <c r="D281" s="10" t="inlineStr">
+        <is>
+          <t>BPM/Tech</t>
+        </is>
+      </c>
+      <c r="E281" s="10" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="F281" s="10" t="n">
+        <v/>
+      </c>
+      <c r="G281" s="12" t="inlineStr">
+        <is>
+          <t>Inactive</t>
+        </is>
+      </c>
+      <c r="H281" s="10" t="inlineStr">
+        <is>
+          <t>Freshers hired via mass drives (NQT/HackWithInfy etc), not this board</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="10" t="inlineStr">
+        <is>
+          <t>Wipro</t>
+        </is>
+      </c>
+      <c r="B282" s="11" t="inlineStr">
+        <is>
+          <t>https://careers.wipro.com/</t>
+        </is>
+      </c>
+      <c r="C282" s="10" t="inlineStr">
+        <is>
+          <t>Indian IT Services</t>
+        </is>
+      </c>
+      <c r="D282" s="10" t="inlineStr">
+        <is>
+          <t>IT Services</t>
+        </is>
+      </c>
+      <c r="E282" s="10" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
+      <c r="F282" s="10" t="n">
+        <v/>
+      </c>
+      <c r="G282" s="12" t="inlineStr">
+        <is>
+          <t>Inactive</t>
+        </is>
+      </c>
+      <c r="H282" s="10" t="inlineStr">
+        <is>
+          <t>Freshers hired via mass drives (NQT/HackWithInfy etc), not this board</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="10" t="inlineStr">
+        <is>
+          <t>Zensar Technologies</t>
+        </is>
+      </c>
+      <c r="B283" s="11" t="inlineStr">
+        <is>
+          <t>https://www.zensar.com/careers</t>
+        </is>
+      </c>
+      <c r="C283" s="10" t="inlineStr">
+        <is>
+          <t>Indian IT Services</t>
+        </is>
+      </c>
+      <c r="D283" s="10" t="inlineStr">
+        <is>
+          <t>IT Services</t>
+        </is>
+      </c>
+      <c r="E283" s="10" t="inlineStr">
+        <is>
+          <t>Pune</t>
+        </is>
+      </c>
+      <c r="F283" s="10" t="n">
+        <v/>
+      </c>
+      <c r="G283" s="10" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="H283" s="10" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="10" t="inlineStr">
+        <is>
+          <t>eInfochips</t>
+        </is>
+      </c>
+      <c r="B284" s="11" t="inlineStr">
+        <is>
+          <t>https://www.einfochips.com/careers/</t>
+        </is>
+      </c>
+      <c r="C284" s="10" t="inlineStr">
+        <is>
+          <t>Indian IT Services</t>
+        </is>
+      </c>
+      <c r="D284" s="10" t="inlineStr">
         <is>
           <t>Engineering Services</t>
         </is>
       </c>
-      <c r="E254" s="9" t="inlineStr">
-        <is>
-          <t>Hyderabad</t>
-        </is>
-      </c>
-      <c r="F254" s="9" t="inlineStr"/>
-      <c r="G254" s="9" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="H254" s="9" t="inlineStr"/>
-    </row>
-    <row r="255">
-      <c r="A255" s="9" t="inlineStr">
-        <is>
-          <t>eInfochips</t>
-        </is>
-      </c>
-      <c r="B255" s="10" t="inlineStr">
-        <is>
-          <t>https://www.einfochips.com/careers/</t>
-        </is>
-      </c>
-      <c r="C255" s="9" t="inlineStr">
-        <is>
-          <t>Indian IT Services</t>
-        </is>
-      </c>
-      <c r="D255" s="9" t="inlineStr">
-        <is>
-          <t>Engineering Services</t>
-        </is>
-      </c>
-      <c r="E255" s="9" t="inlineStr">
+      <c r="E284" s="10" t="inlineStr">
         <is>
           <t>Ahmedabad</t>
         </is>
       </c>
-      <c r="F255" s="9" t="inlineStr"/>
-      <c r="G255" s="9" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="H255" s="9" t="inlineStr"/>
-    </row>
-    <row r="256">
-      <c r="A256" s="9" t="inlineStr">
-        <is>
-          <t>Genpact</t>
-        </is>
-      </c>
-      <c r="B256" s="10" t="inlineStr">
-        <is>
-          <t>https://www.genpact.com/careers</t>
-        </is>
-      </c>
-      <c r="C256" s="9" t="inlineStr">
-        <is>
-          <t>Indian IT Services</t>
-        </is>
-      </c>
-      <c r="D256" s="9" t="inlineStr">
-        <is>
-          <t>BPM/Tech</t>
-        </is>
-      </c>
-      <c r="E256" s="9" t="inlineStr">
-        <is>
-          <t>Gurugram</t>
-        </is>
-      </c>
-      <c r="F256" s="9" t="inlineStr"/>
-      <c r="G256" s="11" t="inlineStr">
-        <is>
-          <t>Inactive</t>
-        </is>
-      </c>
-      <c r="H256" s="9" t="inlineStr">
-        <is>
-          <t>Freshers hired via mass drives (NQT/HackWithInfy etc), not this board</t>
-        </is>
-      </c>
-    </row>
-    <row r="257">
-      <c r="A257" s="9" t="inlineStr">
-        <is>
-          <t>Happiest Minds</t>
-        </is>
-      </c>
-      <c r="B257" s="10" t="inlineStr">
-        <is>
-          <t>https://www.happiestminds.com/careers/</t>
-        </is>
-      </c>
-      <c r="C257" s="9" t="inlineStr">
-        <is>
-          <t>Indian IT Services</t>
-        </is>
-      </c>
-      <c r="D257" s="9" t="inlineStr">
-        <is>
-          <t>IT Services</t>
-        </is>
-      </c>
-      <c r="E257" s="9" t="inlineStr">
-        <is>
-          <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="F257" s="9" t="inlineStr"/>
-      <c r="G257" s="9" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="H257" s="9" t="inlineStr"/>
-    </row>
-    <row r="258">
-      <c r="A258" s="9" t="inlineStr">
-        <is>
-          <t>HCLTech</t>
-        </is>
-      </c>
-      <c r="B258" s="10" t="inlineStr">
-        <is>
-          <t>https://www.hcltech.com/careers</t>
-        </is>
-      </c>
-      <c r="C258" s="9" t="inlineStr">
-        <is>
-          <t>Indian IT Services</t>
-        </is>
-      </c>
-      <c r="D258" s="9" t="inlineStr">
-        <is>
-          <t>IT Services</t>
-        </is>
-      </c>
-      <c r="E258" s="9" t="inlineStr">
-        <is>
-          <t>Noida</t>
-        </is>
-      </c>
-      <c r="F258" s="9" t="inlineStr"/>
-      <c r="G258" s="11" t="inlineStr">
-        <is>
-          <t>Inactive</t>
-        </is>
-      </c>
-      <c r="H258" s="9" t="inlineStr">
-        <is>
-          <t>Freshers hired via mass drives (NQT/HackWithInfy etc), not this board</t>
-        </is>
-      </c>
-    </row>
-    <row r="259">
-      <c r="A259" s="9" t="inlineStr">
-        <is>
-          <t>Hexaware</t>
-        </is>
-      </c>
-      <c r="B259" s="10" t="inlineStr">
-        <is>
-          <t>https://hexaware.com/careers/</t>
-        </is>
-      </c>
-      <c r="C259" s="9" t="inlineStr">
-        <is>
-          <t>Indian IT Services</t>
-        </is>
-      </c>
-      <c r="D259" s="9" t="inlineStr">
-        <is>
-          <t>IT Services</t>
-        </is>
-      </c>
-      <c r="E259" s="9" t="inlineStr">
-        <is>
-          <t>Mumbai</t>
-        </is>
-      </c>
-      <c r="F259" s="9" t="inlineStr"/>
-      <c r="G259" s="9" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="H259" s="9" t="inlineStr"/>
-    </row>
-    <row r="260">
-      <c r="A260" s="9" t="inlineStr">
-        <is>
-          <t>Infosys</t>
-        </is>
-      </c>
-      <c r="B260" s="10" t="inlineStr">
-        <is>
-          <t>https://www.infosys.com/careers/</t>
-        </is>
-      </c>
-      <c r="C260" s="9" t="inlineStr">
-        <is>
-          <t>Indian IT Services</t>
-        </is>
-      </c>
-      <c r="D260" s="9" t="inlineStr">
-        <is>
-          <t>IT Services</t>
-        </is>
-      </c>
-      <c r="E260" s="9" t="inlineStr">
-        <is>
-          <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="F260" s="9" t="inlineStr"/>
-      <c r="G260" s="11" t="inlineStr">
-        <is>
-          <t>Inactive</t>
-        </is>
-      </c>
-      <c r="H260" s="9" t="inlineStr">
-        <is>
-          <t>Freshers hired via mass drives (NQT/HackWithInfy etc), not this board</t>
-        </is>
-      </c>
-    </row>
-    <row r="261">
-      <c r="A261" s="9" t="inlineStr">
-        <is>
-          <t>Infosys BPM</t>
-        </is>
-      </c>
-      <c r="B261" s="10" t="inlineStr">
-        <is>
-          <t>https://www.infosysbpm.com/careers.html</t>
-        </is>
-      </c>
-      <c r="C261" s="9" t="inlineStr">
-        <is>
-          <t>Indian IT Services</t>
-        </is>
-      </c>
-      <c r="D261" s="9" t="inlineStr">
-        <is>
-          <t>BPM/Tech</t>
-        </is>
-      </c>
-      <c r="E261" s="9" t="inlineStr">
-        <is>
-          <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="F261" s="9" t="inlineStr"/>
-      <c r="G261" s="11" t="inlineStr">
-        <is>
-          <t>Inactive</t>
-        </is>
-      </c>
-      <c r="H261" s="9" t="inlineStr">
-        <is>
-          <t>Freshers hired via mass drives (NQT/HackWithInfy etc), not this board</t>
-        </is>
-      </c>
-    </row>
-    <row r="262">
-      <c r="A262" s="9" t="inlineStr">
-        <is>
-          <t>Intellect Design Arena</t>
-        </is>
-      </c>
-      <c r="B262" s="10" t="inlineStr">
-        <is>
-          <t>https://www.intellectdesign.com/careers/</t>
-        </is>
-      </c>
-      <c r="C262" s="9" t="inlineStr">
-        <is>
-          <t>Indian IT Services</t>
-        </is>
-      </c>
-      <c r="D262" s="9" t="inlineStr">
-        <is>
-          <t>FinTech Product</t>
-        </is>
-      </c>
-      <c r="E262" s="9" t="inlineStr">
-        <is>
-          <t>Chennai</t>
-        </is>
-      </c>
-      <c r="F262" s="9" t="inlineStr"/>
-      <c r="G262" s="9" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="H262" s="9" t="inlineStr"/>
-    </row>
-    <row r="263">
-      <c r="A263" s="9" t="inlineStr">
-        <is>
-          <t>KPIT Technologies</t>
-        </is>
-      </c>
-      <c r="B263" s="10" t="inlineStr">
-        <is>
-          <t>https://www.kpit.com/careers/</t>
-        </is>
-      </c>
-      <c r="C263" s="9" t="inlineStr">
-        <is>
-          <t>Indian IT Services</t>
-        </is>
-      </c>
-      <c r="D263" s="9" t="inlineStr">
-        <is>
-          <t>Automotive SW</t>
-        </is>
-      </c>
-      <c r="E263" s="9" t="inlineStr">
-        <is>
-          <t>Pune</t>
-        </is>
-      </c>
-      <c r="F263" s="9" t="inlineStr"/>
-      <c r="G263" s="9" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="H263" s="9" t="inlineStr"/>
-    </row>
-    <row r="264">
-      <c r="A264" s="9" t="inlineStr">
-        <is>
-          <t>L&amp;T Technology Services</t>
-        </is>
-      </c>
-      <c r="B264" s="10" t="inlineStr">
-        <is>
-          <t>https://www.ltts.com/careers</t>
-        </is>
-      </c>
-      <c r="C264" s="9" t="inlineStr">
-        <is>
-          <t>Indian IT Services</t>
-        </is>
-      </c>
-      <c r="D264" s="9" t="inlineStr">
-        <is>
-          <t>Engineering Services</t>
-        </is>
-      </c>
-      <c r="E264" s="9" t="inlineStr">
-        <is>
-          <t>Vadodara</t>
-        </is>
-      </c>
-      <c r="F264" s="9" t="inlineStr"/>
-      <c r="G264" s="9" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="H264" s="9" t="inlineStr"/>
-    </row>
-    <row r="265">
-      <c r="A265" s="9" t="inlineStr">
-        <is>
-          <t>LTIMindtree</t>
-        </is>
-      </c>
-      <c r="B265" s="10" t="inlineStr">
-        <is>
-          <t>https://www.ltimindtree.com/careers/</t>
-        </is>
-      </c>
-      <c r="C265" s="9" t="inlineStr">
-        <is>
-          <t>Indian IT Services</t>
-        </is>
-      </c>
-      <c r="D265" s="9" t="inlineStr">
-        <is>
-          <t>IT Services</t>
-        </is>
-      </c>
-      <c r="E265" s="9" t="inlineStr">
-        <is>
-          <t>Mumbai</t>
-        </is>
-      </c>
-      <c r="F265" s="9" t="inlineStr"/>
-      <c r="G265" s="11" t="inlineStr">
-        <is>
-          <t>Inactive</t>
-        </is>
-      </c>
-      <c r="H265" s="9" t="inlineStr">
-        <is>
-          <t>Freshers hired via mass drives (NQT/HackWithInfy etc), not this board</t>
-        </is>
-      </c>
-    </row>
-    <row r="266">
-      <c r="A266" s="9" t="inlineStr">
-        <is>
-          <t>Mastek</t>
-        </is>
-      </c>
-      <c r="B266" s="10" t="inlineStr">
-        <is>
-          <t>https://www.mastek.com/careers</t>
-        </is>
-      </c>
-      <c r="C266" s="9" t="inlineStr">
-        <is>
-          <t>Indian IT Services</t>
-        </is>
-      </c>
-      <c r="D266" s="9" t="inlineStr">
-        <is>
-          <t>IT Services</t>
-        </is>
-      </c>
-      <c r="E266" s="9" t="inlineStr">
-        <is>
-          <t>Mumbai</t>
-        </is>
-      </c>
-      <c r="F266" s="9" t="inlineStr"/>
-      <c r="G266" s="9" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="H266" s="9" t="inlineStr"/>
-    </row>
-    <row r="267">
-      <c r="A267" s="9" t="inlineStr">
-        <is>
-          <t>Mphasis</t>
-        </is>
-      </c>
-      <c r="B267" s="10" t="inlineStr">
-        <is>
-          <t>https://careers.mphasis.com/</t>
-        </is>
-      </c>
-      <c r="C267" s="9" t="inlineStr">
-        <is>
-          <t>Indian IT Services</t>
-        </is>
-      </c>
-      <c r="D267" s="9" t="inlineStr">
-        <is>
-          <t>IT Services</t>
-        </is>
-      </c>
-      <c r="E267" s="9" t="inlineStr">
-        <is>
-          <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="F267" s="9" t="inlineStr"/>
-      <c r="G267" s="9" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="H267" s="9" t="inlineStr"/>
-    </row>
-    <row r="268">
-      <c r="A268" s="9" t="inlineStr">
-        <is>
-          <t>Newgen Software</t>
-        </is>
-      </c>
-      <c r="B268" s="10" t="inlineStr">
-        <is>
-          <t>https://newgensoft.com/careers/</t>
-        </is>
-      </c>
-      <c r="C268" s="9" t="inlineStr">
-        <is>
-          <t>Indian IT Services</t>
-        </is>
-      </c>
-      <c r="D268" s="9" t="inlineStr">
-        <is>
-          <t>Product/Services</t>
-        </is>
-      </c>
-      <c r="E268" s="9" t="inlineStr">
-        <is>
-          <t>Noida</t>
-        </is>
-      </c>
-      <c r="F268" s="9" t="inlineStr"/>
-      <c r="G268" s="9" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="H268" s="9" t="inlineStr"/>
-    </row>
-    <row r="269">
-      <c r="A269" s="9" t="inlineStr">
-        <is>
-          <t>Nucleus Software</t>
-        </is>
-      </c>
-      <c r="B269" s="10" t="inlineStr">
-        <is>
-          <t>https://www.nucleussoftware.com/careers</t>
-        </is>
-      </c>
-      <c r="C269" s="9" t="inlineStr">
-        <is>
-          <t>Indian IT Services</t>
-        </is>
-      </c>
-      <c r="D269" s="9" t="inlineStr">
-        <is>
-          <t>FinTech Product</t>
-        </is>
-      </c>
-      <c r="E269" s="9" t="inlineStr">
-        <is>
-          <t>Noida</t>
-        </is>
-      </c>
-      <c r="F269" s="9" t="inlineStr"/>
-      <c r="G269" s="9" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="H269" s="9" t="inlineStr"/>
-    </row>
-    <row r="270">
-      <c r="A270" s="9" t="inlineStr">
-        <is>
-          <t>Persistent Systems</t>
-        </is>
-      </c>
-      <c r="B270" s="10" t="inlineStr">
-        <is>
-          <t>https://www.persistent.com/careers/</t>
-        </is>
-      </c>
-      <c r="C270" s="9" t="inlineStr">
-        <is>
-          <t>Indian IT Services</t>
-        </is>
-      </c>
-      <c r="D270" s="9" t="inlineStr">
-        <is>
-          <t>IT Services</t>
-        </is>
-      </c>
-      <c r="E270" s="9" t="inlineStr">
-        <is>
-          <t>Pune</t>
-        </is>
-      </c>
-      <c r="F270" s="9" t="inlineStr"/>
-      <c r="G270" s="9" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="H270" s="9" t="inlineStr"/>
-    </row>
-    <row r="271">
-      <c r="A271" s="9" t="inlineStr">
-        <is>
-          <t>Publicis Sapient India</t>
-        </is>
-      </c>
-      <c r="B271" s="10" t="inlineStr">
-        <is>
-          <t>https://careers.publicissapient.com/</t>
-        </is>
-      </c>
-      <c r="C271" s="9" t="inlineStr">
-        <is>
-          <t>Indian IT Services</t>
-        </is>
-      </c>
-      <c r="D271" s="9" t="inlineStr">
-        <is>
-          <t>Consulting</t>
-        </is>
-      </c>
-      <c r="E271" s="9" t="inlineStr">
-        <is>
-          <t>Gurugram</t>
-        </is>
-      </c>
-      <c r="F271" s="9" t="inlineStr"/>
-      <c r="G271" s="9" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="H271" s="9" t="inlineStr"/>
-    </row>
-    <row r="272">
-      <c r="A272" s="9" t="inlineStr">
-        <is>
-          <t>Qualitest India</t>
-        </is>
-      </c>
-      <c r="B272" s="10" t="inlineStr">
-        <is>
-          <t>https://www.qualitestgroup.com/careers/</t>
-        </is>
-      </c>
-      <c r="C272" s="9" t="inlineStr">
-        <is>
-          <t>Indian IT Services</t>
-        </is>
-      </c>
-      <c r="D272" s="9" t="inlineStr">
-        <is>
-          <t>QA / Testing</t>
-        </is>
-      </c>
-      <c r="E272" s="9" t="inlineStr">
-        <is>
-          <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="F272" s="9" t="inlineStr"/>
-      <c r="G272" s="9" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="H272" s="9" t="inlineStr">
-        <is>
-          <t>Testing-focused - good for QA freshers</t>
-        </is>
-      </c>
-    </row>
-    <row r="273">
-      <c r="A273" s="9" t="inlineStr">
-        <is>
-          <t>Quest Global</t>
-        </is>
-      </c>
-      <c r="B273" s="10" t="inlineStr">
-        <is>
-          <t>https://www.quest-global.com/careers/</t>
-        </is>
-      </c>
-      <c r="C273" s="9" t="inlineStr">
-        <is>
-          <t>Indian IT Services</t>
-        </is>
-      </c>
-      <c r="D273" s="9" t="inlineStr">
-        <is>
-          <t>Engineering Services</t>
-        </is>
-      </c>
-      <c r="E273" s="9" t="inlineStr">
-        <is>
-          <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="F273" s="9" t="inlineStr"/>
-      <c r="G273" s="9" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="H273" s="9" t="inlineStr"/>
-    </row>
-    <row r="274">
-      <c r="A274" s="9" t="inlineStr">
-        <is>
-          <t>Ramco Systems</t>
-        </is>
-      </c>
-      <c r="B274" s="10" t="inlineStr">
-        <is>
-          <t>https://www.ramco.com/careers/</t>
-        </is>
-      </c>
-      <c r="C274" s="9" t="inlineStr">
-        <is>
-          <t>Indian IT Services</t>
-        </is>
-      </c>
-      <c r="D274" s="9" t="inlineStr">
-        <is>
-          <t>Enterprise SW</t>
-        </is>
-      </c>
-      <c r="E274" s="9" t="inlineStr">
-        <is>
-          <t>Chennai</t>
-        </is>
-      </c>
-      <c r="F274" s="9" t="inlineStr"/>
-      <c r="G274" s="9" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="H274" s="9" t="inlineStr"/>
-    </row>
-    <row r="275">
-      <c r="A275" s="9" t="inlineStr">
-        <is>
-          <t>Sasken Technologies</t>
-        </is>
-      </c>
-      <c r="B275" s="10" t="inlineStr">
-        <is>
-          <t>https://www.sasken.com/careers</t>
-        </is>
-      </c>
-      <c r="C275" s="9" t="inlineStr">
-        <is>
-          <t>Indian IT Services</t>
-        </is>
-      </c>
-      <c r="D275" s="9" t="inlineStr">
-        <is>
-          <t>Engineering Services</t>
-        </is>
-      </c>
-      <c r="E275" s="9" t="inlineStr">
-        <is>
-          <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="F275" s="9" t="inlineStr"/>
-      <c r="G275" s="9" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="H275" s="9" t="inlineStr"/>
-    </row>
-    <row r="276">
-      <c r="A276" s="9" t="inlineStr">
-        <is>
-          <t>Sonata Software</t>
-        </is>
-      </c>
-      <c r="B276" s="10" t="inlineStr">
-        <is>
-          <t>https://www.sonata-software.com/careers</t>
-        </is>
-      </c>
-      <c r="C276" s="9" t="inlineStr">
-        <is>
-          <t>Indian IT Services</t>
-        </is>
-      </c>
-      <c r="D276" s="9" t="inlineStr">
-        <is>
-          <t>IT Services</t>
-        </is>
-      </c>
-      <c r="E276" s="9" t="inlineStr">
-        <is>
-          <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="F276" s="9" t="inlineStr"/>
-      <c r="G276" s="9" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="H276" s="9" t="inlineStr"/>
-    </row>
-    <row r="277">
-      <c r="A277" s="9" t="inlineStr">
-        <is>
-          <t>Subex</t>
-        </is>
-      </c>
-      <c r="B277" s="10" t="inlineStr">
-        <is>
-          <t>https://www.subex.com/careers/</t>
-        </is>
-      </c>
-      <c r="C277" s="9" t="inlineStr">
-        <is>
-          <t>Indian IT Services</t>
-        </is>
-      </c>
-      <c r="D277" s="9" t="inlineStr">
-        <is>
-          <t>Telecom SW</t>
-        </is>
-      </c>
-      <c r="E277" s="9" t="inlineStr">
-        <is>
-          <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="F277" s="9" t="inlineStr"/>
-      <c r="G277" s="9" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="H277" s="9" t="inlineStr"/>
-    </row>
-    <row r="278">
-      <c r="A278" s="9" t="inlineStr">
-        <is>
-          <t>Tata Elxsi</t>
-        </is>
-      </c>
-      <c r="B278" s="10" t="inlineStr">
-        <is>
-          <t>https://www.tataelxsi.com/careers</t>
-        </is>
-      </c>
-      <c r="C278" s="9" t="inlineStr">
-        <is>
-          <t>Indian IT Services</t>
-        </is>
-      </c>
-      <c r="D278" s="9" t="inlineStr">
-        <is>
-          <t>Engineering Services</t>
-        </is>
-      </c>
-      <c r="E278" s="9" t="inlineStr">
-        <is>
-          <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="F278" s="9" t="inlineStr"/>
-      <c r="G278" s="9" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="H278" s="9" t="inlineStr"/>
-    </row>
-    <row r="279">
-      <c r="A279" s="9" t="inlineStr">
-        <is>
-          <t>TCS</t>
-        </is>
-      </c>
-      <c r="B279" s="10" t="inlineStr">
-        <is>
-          <t>https://www.tcs.com/careers</t>
-        </is>
-      </c>
-      <c r="C279" s="9" t="inlineStr">
-        <is>
-          <t>Indian IT Services</t>
-        </is>
-      </c>
-      <c r="D279" s="9" t="inlineStr">
-        <is>
-          <t>IT Services</t>
-        </is>
-      </c>
-      <c r="E279" s="9" t="inlineStr">
-        <is>
-          <t>Mumbai</t>
-        </is>
-      </c>
-      <c r="F279" s="9" t="inlineStr"/>
-      <c r="G279" s="11" t="inlineStr">
-        <is>
-          <t>Inactive</t>
-        </is>
-      </c>
-      <c r="H279" s="9" t="inlineStr">
-        <is>
-          <t>Freshers hired via mass drives (NQT/HackWithInfy etc), not this board</t>
-        </is>
-      </c>
-    </row>
-    <row r="280">
-      <c r="A280" s="9" t="inlineStr">
-        <is>
-          <t>Tech Mahindra</t>
-        </is>
-      </c>
-      <c r="B280" s="10" t="inlineStr">
-        <is>
-          <t>https://careers.techmahindra.com/</t>
-        </is>
-      </c>
-      <c r="C280" s="9" t="inlineStr">
-        <is>
-          <t>Indian IT Services</t>
-        </is>
-      </c>
-      <c r="D280" s="9" t="inlineStr">
-        <is>
-          <t>IT Services</t>
-        </is>
-      </c>
-      <c r="E280" s="9" t="inlineStr">
-        <is>
-          <t>Pune</t>
-        </is>
-      </c>
-      <c r="F280" s="9" t="inlineStr"/>
-      <c r="G280" s="11" t="inlineStr">
-        <is>
-          <t>Inactive</t>
-        </is>
-      </c>
-      <c r="H280" s="9" t="inlineStr">
-        <is>
-          <t>Freshers hired via mass drives (NQT/HackWithInfy etc), not this board</t>
-        </is>
-      </c>
-    </row>
-    <row r="281">
-      <c r="A281" s="9" t="inlineStr">
-        <is>
-          <t>Thoughtworks India</t>
-        </is>
-      </c>
-      <c r="B281" s="10" t="inlineStr">
-        <is>
-          <t>https://www.thoughtworks.com/careers/jobs</t>
-        </is>
-      </c>
-      <c r="C281" s="9" t="inlineStr">
-        <is>
-          <t>Indian IT Services</t>
-        </is>
-      </c>
-      <c r="D281" s="9" t="inlineStr">
-        <is>
-          <t>Consulting</t>
-        </is>
-      </c>
-      <c r="E281" s="9" t="inlineStr">
-        <is>
-          <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="F281" s="9" t="inlineStr"/>
-      <c r="G281" s="9" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="H281" s="9" t="inlineStr"/>
-    </row>
-    <row r="282">
-      <c r="A282" s="9" t="inlineStr">
-        <is>
-          <t>Wipro</t>
-        </is>
-      </c>
-      <c r="B282" s="10" t="inlineStr">
-        <is>
-          <t>https://careers.wipro.com/</t>
-        </is>
-      </c>
-      <c r="C282" s="9" t="inlineStr">
-        <is>
-          <t>Indian IT Services</t>
-        </is>
-      </c>
-      <c r="D282" s="9" t="inlineStr">
-        <is>
-          <t>IT Services</t>
-        </is>
-      </c>
-      <c r="E282" s="9" t="inlineStr">
-        <is>
-          <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="F282" s="9" t="inlineStr"/>
-      <c r="G282" s="11" t="inlineStr">
-        <is>
-          <t>Inactive</t>
-        </is>
-      </c>
-      <c r="H282" s="9" t="inlineStr">
-        <is>
-          <t>Freshers hired via mass drives (NQT/HackWithInfy etc), not this board</t>
-        </is>
-      </c>
-    </row>
-    <row r="283">
-      <c r="A283" s="9" t="inlineStr">
-        <is>
-          <t>WNS Global</t>
-        </is>
-      </c>
-      <c r="B283" s="10" t="inlineStr">
-        <is>
-          <t>https://www.wns.com/careers</t>
-        </is>
-      </c>
-      <c r="C283" s="9" t="inlineStr">
-        <is>
-          <t>Indian IT Services</t>
-        </is>
-      </c>
-      <c r="D283" s="9" t="inlineStr">
-        <is>
-          <t>BPM/Tech</t>
-        </is>
-      </c>
-      <c r="E283" s="9" t="inlineStr">
-        <is>
-          <t>Mumbai</t>
-        </is>
-      </c>
-      <c r="F283" s="9" t="inlineStr"/>
-      <c r="G283" s="11" t="inlineStr">
-        <is>
-          <t>Inactive</t>
-        </is>
-      </c>
-      <c r="H283" s="9" t="inlineStr">
-        <is>
-          <t>Freshers hired via mass drives (NQT/HackWithInfy etc), not this board</t>
-        </is>
-      </c>
-    </row>
-    <row r="284">
-      <c r="A284" s="9" t="inlineStr">
-        <is>
-          <t>Zensar Technologies</t>
-        </is>
-      </c>
-      <c r="B284" s="10" t="inlineStr">
-        <is>
-          <t>https://www.zensar.com/careers</t>
-        </is>
-      </c>
-      <c r="C284" s="9" t="inlineStr">
-        <is>
-          <t>Indian IT Services</t>
-        </is>
-      </c>
-      <c r="D284" s="9" t="inlineStr">
-        <is>
-          <t>IT Services</t>
-        </is>
-      </c>
-      <c r="E284" s="9" t="inlineStr">
-        <is>
-          <t>Pune</t>
-        </is>
-      </c>
-      <c r="F284" s="9" t="inlineStr"/>
-      <c r="G284" s="9" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="H284" s="9" t="inlineStr"/>
+      <c r="F284" s="10" t="n">
+        <v/>
+      </c>
+      <c r="G284" s="10" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="H284" s="10" t="n">
+        <v/>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:H284"/>
@@ -10758,192 +11866,140 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A29"/>
+  <dimension ref="A1:A21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="12" t="inlineStr">
-        <is>
-          <t>HOW TO USE THIS FILE</t>
+      <c r="A1" s="14" t="inlineStr">
+        <is>
+          <t>WHAT CHANGED IN THIS VERSION</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="inlineStr"/>
+      <c r="A2" s="15" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
-        <is>
-          <t>The 'Companies' sheet MUST stay as the first tab - main.py reads sheet 1 only.</t>
+      <c r="A3" s="15" t="inlineStr">
+        <is>
+          <t>50 companies had their Careers URL swapped to a verified ATS board (Greenhouse, Lever,</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr"/>
+      <c r="A4" s="15" t="inlineStr">
+        <is>
+          <t>Ashby, SmartRecruiters, Workable, or Recruitee), confirmed by actually calling that API and</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="12" t="inlineStr">
-        <is>
-          <t>SEE TYPES SEPARATELY</t>
+      <c r="A5" s="15" t="inlineStr">
+        <is>
+          <t>checking it returned real jobs.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="inlineStr">
-        <is>
-          <t>Click the filter arrow on the 'Type' column header. Colours also separate them:</t>
-        </is>
-      </c>
+      <c r="A6" s="15" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   green = Startup     blue = Unicorn/Scaleup     orange = MNC (GCC)     purple = Indian IT Services</t>
+      <c r="A7" s="15" t="inlineStr">
+        <is>
+          <t>5 companies were flipped from Inactive back to Active because a working board was found:</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="13" t="inlineStr">
-        <is>
-          <t>They are kept on one sheet on purpose. Splitting into tabs would mean main.py</t>
+      <c r="A8" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   TCS, Continental India, Western Digital India, Accenture India, Genpact</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="13" t="inlineStr">
-        <is>
-          <t>only ever reads one of them, and duplicated rows drift out of sync as you edit.</t>
-        </is>
-      </c>
+      <c r="A9" s="15" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="13" t="inlineStr"/>
+      <c r="A10" s="14" t="inlineStr">
+        <is>
+          <t>8 companies were left UNCHANGED despite the audit marking them Verified - the auto-guesser</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="12" t="inlineStr">
-        <is>
-          <t>IMPORTANT - THE URLs ARE STARTING POINTS, NOT VERIFIED</t>
+      <c r="A11" s="15" t="inlineStr">
+        <is>
+          <t>made a mistake on these and I am not confident the URL is really theirs:</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="13" t="inlineStr">
-        <is>
-          <t>These are each company's own careers page. Only Postman is a confirmed ATS board URL.</t>
+      <c r="A12" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Boeing India, Dell Technologies India, GE Aerospace India, HP India, Intel India,</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="13" t="inlineStr">
-        <is>
-          <t>Run this first, before anything else:</t>
+      <c r="A13" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Lowe's India, SAP Labs India, Siemens India</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        python discover.py --audit</t>
+      <c r="A14" s="15" t="inlineStr">
+        <is>
+          <t>Why: their current careers URLs all start with "jobs.company.com", and the token-guesser</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="13" t="inlineStr">
-        <is>
-          <t>It checks every row, finds which sit on a supported ATS (Greenhouse / Lever / Ashby /</t>
+      <c r="A15" s="15" t="inlineStr">
+        <is>
+          <t>grabbed the word "jobs" itself as the guess instead of the company name. That happened to</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="13" t="inlineStr">
-        <is>
-          <t>SmartRecruiters / Workable / Recruitee), and writes reports/company_audit.xlsx with a</t>
+      <c r="A16" s="15" t="inlineStr">
+        <is>
+          <t>resolve to a generic Recruitee demo board, not the real company. Left as-is (Workday/Taleo,</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="13" t="inlineStr">
-        <is>
-          <t>'Suggested URL' column. Paste those back into column B. Expect roughly 40-60% to resolve.</t>
+      <c r="A17" s="15" t="inlineStr">
+        <is>
+          <t>not scraped) rather than risk feeding the tracker a wrong board.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="13" t="inlineStr"/>
+      <c r="A18" s="15" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="12" t="inlineStr">
-        <is>
-          <t>WHY 62 ROWS ARE ALREADY INACTIVE</t>
+      <c r="A19" s="14" t="inlineStr">
+        <is>
+          <t>4 rows are marked in gold - TCS, Continental India, Genpact, Western Digital India. These DID</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="13" t="inlineStr">
-        <is>
-          <t>Most large MNCs run Workday, Taleo or SuccessFactors. This scraper does not support them,</t>
+      <c r="A20" s="15" t="inlineStr">
+        <is>
+          <t>get a specific, plausible token and were updated, but I could not independently re-verify them</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="13" t="inlineStr">
-        <is>
-          <t>so those rows would fail every single day and slow the run down for nothing.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="13" t="inlineStr">
-        <is>
-          <t>Most Indian IT services giants hire freshers through mass drives (TCS NQT, Infosys</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="13" t="inlineStr">
-        <is>
-          <t>HackWithInfy, Wipro Elite NLTH, Cognizant GenC) rather than posting on these boards.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="13" t="inlineStr">
-        <is>
-          <t>Watch those separately - a scraper will not catch them.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="13" t="inlineStr">
-        <is>
-          <t>Set Status back to Active for any row the audit proves works.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="13" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="12" t="inlineStr">
-        <is>
-          <t>ADDING YOUR OWN</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="13" t="inlineStr">
-        <is>
-          <t>Only 'Company Name' and 'Careers URL' are required. Everything else is for your own use.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="13" t="inlineStr">
-        <is>
-          <t>Check a single new company before adding it:   python discover.py https://theirsite.com/careers</t>
+      <c r="A21" s="15" t="inlineStr">
+        <is>
+          <t>from this environment. Worth a glance once their first email arrives.</t>
         </is>
       </c>
     </row>
